--- a/Übungen/Onlineshop.xlsx
+++ b/Übungen/Onlineshop.xlsx
@@ -5,11 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="PSP" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="Netzplan" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Gantt" sheetId="3" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="81">
   <si>
     <t xml:space="preserve">Beispiel: Funktionsorientierter Projektstrukturplan</t>
   </si>
@@ -183,9 +184,18 @@
     <t xml:space="preserve">1.1.1, 1.2.2</t>
   </si>
   <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.1.2, 1.1.3</t>
   </si>
   <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.2.4, 1.3.1</t>
   </si>
   <si>
@@ -247,20 +257,30 @@
   </si>
   <si>
     <t xml:space="preserve">FAZ + D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Datenbankvorbereitung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Testphase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gantt</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
     <numFmt numFmtId="166" formatCode="@"/>
     <numFmt numFmtId="167" formatCode="0.00\ %"/>
     <numFmt numFmtId="168" formatCode="General"/>
+    <numFmt numFmtId="169" formatCode="0\ %"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="13">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -319,8 +339,36 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF127622"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF55308D"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF8000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFDDDDDD"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -348,7 +396,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFAADCF7"/>
-        <bgColor rgb="FFCCCCFF"/>
+        <bgColor rgb="FFDDDDDD"/>
       </patternFill>
     </fill>
     <fill>
@@ -360,13 +408,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00A933"/>
-        <bgColor rgb="FF008000"/>
+        <bgColor rgb="FF008080"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF8000"/>
         <bgColor rgb="FFFF6600"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFEEEEEE"/>
       </patternFill>
     </fill>
   </fills>
@@ -483,7 +537,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="81">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -624,10 +678,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -660,10 +710,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -684,10 +730,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -730,6 +772,94 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="70" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="70" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -744,7 +874,7 @@
     <cellStyle name="KritischerPfad" xfId="21"/>
     <cellStyle name="Wochenende" xfId="22"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="4">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -753,6 +883,48 @@
         <b val="1"/>
         <color rgb="FFFF0000"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="2"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF666666"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="2"/>
+        <b val="1"/>
+        <i val="0"/>
+        <color rgb="FFFFFFFF"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCC0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="2"/>
+        <color rgb="FFFFBF00"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFBF00"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <colors>
@@ -765,8 +937,8 @@
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FFCC0000"/>
+      <rgbColor rgb="FF127622"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
@@ -780,7 +952,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFDDDDDD"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -811,7 +983,7 @@
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF55308D"/>
       <rgbColor rgb="FF333333"/>
     </indexedColors>
   </colors>
@@ -823,13 +995,13 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>907920</xdr:colOff>
+      <xdr:colOff>908280</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>154440</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>12240</xdr:colOff>
+      <xdr:colOff>12600</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>154440</xdr:rowOff>
     </xdr:to>
@@ -840,8 +1012,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="5499000" y="479520"/>
-          <a:ext cx="5563080" cy="0"/>
+          <a:off x="5511960" y="479520"/>
+          <a:ext cx="5585400" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -882,7 +1054,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5498280" y="488160"/>
+          <a:off x="5510880" y="488160"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -923,7 +1095,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5497560" y="488160"/>
+          <a:off x="5510160" y="488160"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -965,7 +1137,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5514120" y="1125360"/>
+          <a:off x="5529960" y="1125360"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1007,7 +1179,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5514120" y="1612800"/>
+          <a:off x="5529960" y="1612800"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1049,7 +1221,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5514120" y="2099880"/>
+          <a:off x="5529960" y="2099880"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1091,7 +1263,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5514120" y="2587320"/>
+          <a:off x="5529960" y="2587320"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1133,7 +1305,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8282160" y="324720"/>
+          <a:off x="8307360" y="324720"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1175,7 +1347,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8282160" y="487440"/>
+          <a:off x="8307360" y="487440"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1217,7 +1389,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8282160" y="1125360"/>
+          <a:off x="8307360" y="1125360"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1259,7 +1431,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8282160" y="1612800"/>
+          <a:off x="8307360" y="1612800"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1301,7 +1473,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8282160" y="2587320"/>
+          <a:off x="8307360" y="2587320"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1343,7 +1515,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8282160" y="3074400"/>
+          <a:off x="8307360" y="3074400"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1385,7 +1557,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8282160" y="4048920"/>
+          <a:off x="8307360" y="4048920"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1427,7 +1599,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8282160" y="5023440"/>
+          <a:off x="8307360" y="5023440"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1469,7 +1641,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11050560" y="487440"/>
+          <a:off x="11085480" y="487440"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1511,7 +1683,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11050560" y="1125360"/>
+          <a:off x="11085480" y="1125360"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1553,7 +1725,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11050560" y="1612800"/>
+          <a:off x="11085480" y="1612800"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1595,7 +1767,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11050560" y="2099880"/>
+          <a:off x="11085480" y="2099880"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1637,7 +1809,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8270640" y="3557520"/>
+          <a:off x="8292960" y="3557520"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1679,7 +1851,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8270640" y="4533480"/>
+          <a:off x="8292960" y="4533480"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1721,7 +1893,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8270640" y="2093760"/>
+          <a:off x="8292960" y="2093760"/>
           <a:ext cx="0" cy="170640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1746,17 +1918,13 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M41"/>
-  <sheetFormatPr defaultColWidth="13.09375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="13.13671875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.77"/>
   </cols>
@@ -2298,12 +2466,14 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:BW35"/>
-  <sheetFormatPr defaultColWidth="11.83984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.89453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="1"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="20" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="3" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="2" min="2" style="20" width="11.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="3" min="3" style="0" width="13.52"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="4" min="4" style="0" width="11.81"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="5" min="5" style="3" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="6" min="6" style="3" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="3" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="21" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="3" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="107" min="11" style="0" width="3.83"/>
@@ -2353,8 +2523,8 @@
       <c r="G2" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="H2" s="28" t="n">
-        <v>3</v>
+      <c r="H2" s="27" t="s">
+        <v>53</v>
       </c>
       <c r="I2" s="29" t="n">
         <v>1</v>
@@ -2387,20 +2557,20 @@
       <c r="W2" s="31"/>
       <c r="X2" s="30" t="n">
         <f aca="false">V2+V4</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL2" s="30" t="n">
         <f aca="false">MAX(X2,AC8,X14)</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AM2" s="31"/>
       <c r="AN2" s="30" t="n">
         <f aca="false">AL2+AL4</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ2" s="30" t="n">
         <f aca="false">AN2</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR2" s="31"/>
       <c r="AS2" s="30" t="n">
@@ -2414,52 +2584,52 @@
       <c r="AW2" s="31"/>
       <c r="AX2" s="30" t="n">
         <f aca="false">AV2+AV4</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA2" s="30" t="n">
         <f aca="false">AX2</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB2" s="31"/>
       <c r="BC2" s="30" t="n">
         <f aca="false">BA2+BA4</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BF2" s="30" t="n">
         <f aca="false">BC2</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BG2" s="31"/>
       <c r="BH2" s="30" t="n">
         <f aca="false">BF2+BF4</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BK2" s="30" t="n">
         <f aca="false">BH2</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BL2" s="31"/>
       <c r="BM2" s="30" t="n">
         <f aca="false">BK2+BK4</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BP2" s="30" t="n">
         <f aca="false">BM2</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BQ2" s="31"/>
       <c r="BR2" s="30" t="n">
         <f aca="false">BP2+BP4</f>
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BU2" s="30" t="n">
         <f aca="false">MAX(BR2,AN14)</f>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BV2" s="31"/>
       <c r="BW2" s="30" t="n">
         <f aca="false">BU2+BU4</f>
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2475,76 +2645,76 @@
         <v>16</v>
       </c>
       <c r="F3" s="33" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G3" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="H3" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="35" t="n">
+      <c r="H3" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3" s="29" t="n">
         <v>1</v>
       </c>
       <c r="J3" s="28" t="n">
         <f aca="false">ROUNDUP(G3/(H3*I3),0)</f>
         <v>1</v>
       </c>
-      <c r="L3" s="36" t="s">
+      <c r="L3" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="36"/>
-      <c r="N3" s="36"/>
-      <c r="Q3" s="36" t="s">
+      <c r="M3" s="35"/>
+      <c r="N3" s="35"/>
+      <c r="Q3" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="36"/>
-      <c r="S3" s="36"/>
-      <c r="V3" s="36" t="s">
+      <c r="R3" s="35"/>
+      <c r="S3" s="35"/>
+      <c r="V3" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="W3" s="36"/>
-      <c r="X3" s="36"/>
-      <c r="AL3" s="36" t="s">
+      <c r="W3" s="35"/>
+      <c r="X3" s="35"/>
+      <c r="AL3" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="AM3" s="36"/>
-      <c r="AN3" s="36"/>
-      <c r="AQ3" s="36" t="s">
+      <c r="AM3" s="35"/>
+      <c r="AN3" s="35"/>
+      <c r="AQ3" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="AR3" s="36"/>
-      <c r="AS3" s="36"/>
-      <c r="AV3" s="36" t="s">
+      <c r="AR3" s="35"/>
+      <c r="AS3" s="35"/>
+      <c r="AV3" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="AW3" s="36"/>
-      <c r="AX3" s="36"/>
-      <c r="BA3" s="36" t="s">
+      <c r="AW3" s="35"/>
+      <c r="AX3" s="35"/>
+      <c r="BA3" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="BB3" s="36"/>
-      <c r="BC3" s="36"/>
-      <c r="BF3" s="36" t="s">
+      <c r="BB3" s="35"/>
+      <c r="BC3" s="35"/>
+      <c r="BF3" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="BG3" s="36"/>
-      <c r="BH3" s="36"/>
-      <c r="BK3" s="36" t="s">
+      <c r="BG3" s="35"/>
+      <c r="BH3" s="35"/>
+      <c r="BK3" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="BL3" s="36"/>
-      <c r="BM3" s="36"/>
-      <c r="BP3" s="36" t="s">
+      <c r="BL3" s="35"/>
+      <c r="BM3" s="35"/>
+      <c r="BP3" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="BQ3" s="36"/>
-      <c r="BR3" s="36"/>
-      <c r="BU3" s="36" t="s">
+      <c r="BQ3" s="35"/>
+      <c r="BR3" s="35"/>
+      <c r="BU3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="BV3" s="36"/>
-      <c r="BW3" s="36"/>
+      <c r="BV3" s="35"/>
+      <c r="BW3" s="35"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
@@ -2564,176 +2734,176 @@
       <c r="G4" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="H4" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="35" t="n">
-        <v>0.6</v>
+      <c r="H4" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="I4" s="29" t="n">
+        <v>0.75</v>
       </c>
       <c r="J4" s="28" t="n">
         <f aca="false">ROUNDUP(G4/(H4*I4),0)</f>
-        <v>7</v>
-      </c>
-      <c r="L4" s="37" t="n">
+        <v>6</v>
+      </c>
+      <c r="L4" s="36" t="n">
         <f aca="false">J2</f>
         <v>2</v>
       </c>
-      <c r="M4" s="38" t="n">
+      <c r="M4" s="37" t="n">
         <f aca="false">N5-N2</f>
         <v>0</v>
       </c>
-      <c r="N4" s="37" t="n">
+      <c r="N4" s="36" t="n">
         <f aca="false">MIN(Q2,Q14)-N2</f>
         <v>0</v>
       </c>
-      <c r="O4" s="39"/>
-      <c r="P4" s="40"/>
-      <c r="Q4" s="37" t="n">
+      <c r="O4" s="38"/>
+      <c r="P4" s="39"/>
+      <c r="Q4" s="36" t="n">
         <f aca="false">J3</f>
         <v>1</v>
       </c>
-      <c r="R4" s="38" t="n">
+      <c r="R4" s="37" t="n">
         <f aca="false">S5-S2</f>
         <v>5</v>
       </c>
-      <c r="S4" s="37" t="n">
-        <f aca="false">V2-S2</f>
+      <c r="S4" s="36" t="n">
+        <f aca="false">MIN(V2,V8)-S2</f>
         <v>0</v>
       </c>
-      <c r="T4" s="39"/>
-      <c r="U4" s="40"/>
-      <c r="V4" s="37" t="n">
+      <c r="T4" s="38"/>
+      <c r="U4" s="39"/>
+      <c r="V4" s="36" t="n">
         <f aca="false">J4</f>
-        <v>7</v>
-      </c>
-      <c r="W4" s="38" t="n">
+        <v>6</v>
+      </c>
+      <c r="W4" s="37" t="n">
         <f aca="false">X5-X2</f>
-        <v>6</v>
-      </c>
-      <c r="X4" s="37" t="n">
+        <v>5</v>
+      </c>
+      <c r="X4" s="36" t="n">
         <f aca="false">AL2-X2</f>
-        <v>1</v>
-      </c>
-      <c r="Y4" s="39"/>
-      <c r="Z4" s="39"/>
-      <c r="AA4" s="39"/>
-      <c r="AB4" s="39"/>
-      <c r="AC4" s="39"/>
-      <c r="AD4" s="39"/>
-      <c r="AE4" s="39"/>
-      <c r="AF4" s="39"/>
-      <c r="AG4" s="39"/>
-      <c r="AH4" s="39"/>
-      <c r="AI4" s="39"/>
-      <c r="AJ4" s="39"/>
-      <c r="AK4" s="40"/>
-      <c r="AL4" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="38"/>
+      <c r="Z4" s="38"/>
+      <c r="AA4" s="38"/>
+      <c r="AB4" s="38"/>
+      <c r="AC4" s="38"/>
+      <c r="AD4" s="38"/>
+      <c r="AE4" s="38"/>
+      <c r="AF4" s="38"/>
+      <c r="AG4" s="38"/>
+      <c r="AH4" s="38"/>
+      <c r="AI4" s="38"/>
+      <c r="AJ4" s="38"/>
+      <c r="AK4" s="39"/>
+      <c r="AL4" s="36" t="n">
         <f aca="false">J9</f>
-        <v>1</v>
-      </c>
-      <c r="AM4" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM4" s="37" t="n">
         <f aca="false">AN5-AN2</f>
         <v>5</v>
       </c>
-      <c r="AN4" s="38" t="n">
-        <f aca="false">AO5-AO2</f>
+      <c r="AN4" s="36" t="n">
+        <f aca="false">AQ2-AN2</f>
         <v>0</v>
       </c>
-      <c r="AO4" s="39"/>
-      <c r="AP4" s="39"/>
-      <c r="AQ4" s="37" t="n">
+      <c r="AO4" s="38"/>
+      <c r="AP4" s="38"/>
+      <c r="AQ4" s="36" t="n">
         <f aca="false">J10</f>
-        <v>1</v>
-      </c>
-      <c r="AR4" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR4" s="37" t="n">
         <f aca="false">AS5-AS2</f>
         <v>5</v>
       </c>
-      <c r="AS4" s="38" t="n">
-        <f aca="false">AT5-AT2</f>
+      <c r="AS4" s="36" t="n">
+        <f aca="false">AV2-AS2</f>
         <v>0</v>
       </c>
-      <c r="AT4" s="39"/>
-      <c r="AU4" s="39"/>
-      <c r="AV4" s="37" t="n">
+      <c r="AT4" s="38"/>
+      <c r="AU4" s="38"/>
+      <c r="AV4" s="36" t="n">
         <f aca="false">J11</f>
-        <v>1</v>
-      </c>
-      <c r="AW4" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW4" s="37" t="n">
         <f aca="false">AX5-AX2</f>
         <v>5</v>
       </c>
-      <c r="AX4" s="38" t="n">
-        <f aca="false">AY5-AY2</f>
+      <c r="AX4" s="36" t="n">
+        <f aca="false">BA2-AX2</f>
         <v>0</v>
       </c>
-      <c r="AY4" s="39"/>
-      <c r="AZ4" s="39"/>
-      <c r="BA4" s="37" t="n">
+      <c r="AY4" s="38"/>
+      <c r="AZ4" s="38"/>
+      <c r="BA4" s="36" t="n">
         <f aca="false">J13</f>
         <v>2</v>
       </c>
-      <c r="BB4" s="38" t="n">
+      <c r="BB4" s="37" t="n">
         <f aca="false">BC5-BC2</f>
         <v>5</v>
       </c>
-      <c r="BC4" s="38" t="n">
-        <f aca="false">BD5-BD2</f>
+      <c r="BC4" s="36" t="n">
+        <f aca="false">BF2-BC2</f>
         <v>0</v>
       </c>
-      <c r="BD4" s="39"/>
-      <c r="BE4" s="39"/>
-      <c r="BF4" s="37" t="n">
+      <c r="BD4" s="38"/>
+      <c r="BE4" s="38"/>
+      <c r="BF4" s="36" t="n">
         <f aca="false">J14</f>
         <v>2</v>
       </c>
-      <c r="BG4" s="38" t="n">
+      <c r="BG4" s="37" t="n">
         <f aca="false">BH5-BH2</f>
         <v>5</v>
       </c>
-      <c r="BH4" s="38" t="n">
-        <f aca="false">BI5-BI2</f>
+      <c r="BH4" s="36" t="n">
+        <f aca="false">BK2-BH2</f>
         <v>0</v>
       </c>
-      <c r="BI4" s="39"/>
-      <c r="BJ4" s="39"/>
-      <c r="BK4" s="37" t="n">
+      <c r="BI4" s="38"/>
+      <c r="BJ4" s="38"/>
+      <c r="BK4" s="36" t="n">
         <f aca="false">J15</f>
         <v>1</v>
       </c>
-      <c r="BL4" s="38" t="n">
+      <c r="BL4" s="37" t="n">
         <f aca="false">BM5-BM2</f>
         <v>5</v>
       </c>
-      <c r="BM4" s="38" t="n">
-        <f aca="false">BN5-BN2</f>
+      <c r="BM4" s="36" t="n">
+        <f aca="false">BP2-BM2</f>
         <v>0</v>
       </c>
-      <c r="BN4" s="39"/>
-      <c r="BO4" s="39"/>
-      <c r="BP4" s="37" t="n">
+      <c r="BN4" s="38"/>
+      <c r="BO4" s="38"/>
+      <c r="BP4" s="36" t="n">
         <f aca="false">J16</f>
-        <v>2</v>
-      </c>
-      <c r="BQ4" s="38" t="n">
+        <v>4</v>
+      </c>
+      <c r="BQ4" s="37" t="n">
         <f aca="false">BR5-BR2</f>
         <v>5</v>
       </c>
-      <c r="BR4" s="37" t="n">
+      <c r="BR4" s="36" t="n">
         <f aca="false">BU2-BR2</f>
         <v>5</v>
       </c>
-      <c r="BS4" s="39"/>
-      <c r="BT4" s="40"/>
-      <c r="BU4" s="37" t="n">
+      <c r="BS4" s="38"/>
+      <c r="BT4" s="39"/>
+      <c r="BU4" s="36" t="n">
         <f aca="false">J17</f>
         <v>1</v>
       </c>
-      <c r="BV4" s="38" t="n">
+      <c r="BV4" s="37" t="n">
         <f aca="false">BW5-BW2</f>
         <v>0</v>
       </c>
-      <c r="BW4" s="37"/>
+      <c r="BW4" s="36"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
@@ -2753,16 +2923,16 @@
       <c r="G5" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="H5" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" s="35" t="n">
-        <f aca="false">(100%+(100%-$I$4))/2</f>
-        <v>0.7</v>
+      <c r="H5" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="I5" s="29" t="n">
+        <f aca="false">(100%+50%+25%)/3</f>
+        <v>0.583333333333333</v>
       </c>
       <c r="J5" s="28" t="n">
         <f aca="false">ROUNDUP(G5/(H5*I5),0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L5" s="30" t="n">
         <v>0</v>
@@ -2772,39 +2942,39 @@
         <f aca="false">MIN(Q5,Q17)</f>
         <v>2</v>
       </c>
-      <c r="P5" s="41"/>
+      <c r="P5" s="40"/>
       <c r="Q5" s="30" t="n">
         <f aca="false">S5-Q4</f>
         <v>7</v>
       </c>
       <c r="R5" s="31"/>
       <c r="S5" s="30" t="n">
-        <f aca="false">MIN(V11,V5)</f>
+        <f aca="false">MIN(V5,V11)</f>
         <v>8</v>
       </c>
-      <c r="U5" s="41"/>
+      <c r="U5" s="40"/>
       <c r="V5" s="30" t="n">
         <f aca="false">X5-V4</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W5" s="31"/>
       <c r="X5" s="30" t="n">
         <f aca="false">AL5</f>
-        <v>16</v>
-      </c>
-      <c r="AK5" s="41"/>
+        <v>14</v>
+      </c>
+      <c r="AK5" s="40"/>
       <c r="AL5" s="30" t="n">
         <f aca="false">AN5-AL4</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AM5" s="31"/>
       <c r="AN5" s="30" t="n">
         <f aca="false">AQ5</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ5" s="30" t="n">
         <f aca="false">AS5-AQ4</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR5" s="31"/>
       <c r="AS5" s="30" t="n">
@@ -2818,53 +2988,53 @@
       <c r="AW5" s="31"/>
       <c r="AX5" s="30" t="n">
         <f aca="false">BA5</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA5" s="30" t="n">
         <f aca="false">BC5-BA4</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB5" s="31"/>
       <c r="BC5" s="30" t="n">
         <f aca="false">BF5</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BF5" s="30" t="n">
         <f aca="false">BH5-BF4</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BG5" s="31"/>
       <c r="BH5" s="30" t="n">
         <f aca="false">BK5</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BK5" s="30" t="n">
         <f aca="false">BM5-BK4</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BL5" s="31"/>
       <c r="BM5" s="30" t="n">
         <f aca="false">BP5</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BP5" s="30" t="n">
         <f aca="false">BR5-BP4</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BQ5" s="31"/>
       <c r="BR5" s="30" t="n">
         <f aca="false">BU5</f>
-        <v>26</v>
-      </c>
-      <c r="BT5" s="41"/>
+        <v>29</v>
+      </c>
+      <c r="BT5" s="40"/>
       <c r="BU5" s="30" t="n">
         <f aca="false">BW5-BU4</f>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BV5" s="31"/>
       <c r="BW5" s="30" t="n">
         <f aca="false">BW2</f>
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2876,30 +3046,30 @@
       </c>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
-      <c r="E6" s="42" t="s">
+      <c r="E6" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="42" t="s">
+      <c r="F6" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="43" t="n">
+      <c r="G6" s="42" t="n">
         <v>7</v>
       </c>
-      <c r="H6" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" s="35" t="n">
-        <f aca="false">(100%+(100%-$I$4))/2</f>
-        <v>0.7</v>
+      <c r="H6" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="I6" s="29" t="n">
+        <f aca="false">(100%+50%+25%)/3</f>
+        <v>0.583333333333333</v>
       </c>
       <c r="J6" s="28" t="n">
         <f aca="false">ROUNDUP(G6/(H6*I6),0)</f>
-        <v>5</v>
-      </c>
-      <c r="P6" s="41"/>
-      <c r="U6" s="41"/>
-      <c r="AK6" s="41"/>
-      <c r="BT6" s="41"/>
+        <v>4</v>
+      </c>
+      <c r="P6" s="40"/>
+      <c r="U6" s="40"/>
+      <c r="AK6" s="40"/>
+      <c r="BT6" s="40"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
@@ -2919,20 +3089,20 @@
       <c r="G7" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="43" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" s="44" t="n">
+      <c r="H7" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="I7" s="29" t="n">
         <v>1</v>
       </c>
       <c r="J7" s="28" t="n">
         <f aca="false">ROUNDUP(G7/(H7*I7),0)</f>
         <v>1</v>
       </c>
-      <c r="P7" s="41"/>
-      <c r="U7" s="41"/>
-      <c r="AK7" s="41"/>
-      <c r="BT7" s="41"/>
+      <c r="P7" s="40"/>
+      <c r="U7" s="40"/>
+      <c r="AK7" s="40"/>
+      <c r="BT7" s="40"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
@@ -2943,27 +3113,27 @@
       </c>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
-      <c r="E8" s="42" t="s">
+      <c r="E8" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="42" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8" s="43" t="n">
+      <c r="F8" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="H8" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="44" t="n">
-        <v>1</v>
+      <c r="H8" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8" s="29" t="n">
+        <v>0.5</v>
       </c>
       <c r="J8" s="28" t="n">
         <f aca="false">ROUNDUP(G8/(H8*I8),0)</f>
-        <v>3</v>
-      </c>
-      <c r="P8" s="41"/>
-      <c r="U8" s="41"/>
+        <v>6</v>
+      </c>
+      <c r="P8" s="40"/>
+      <c r="U8" s="40"/>
       <c r="V8" s="30" t="n">
         <f aca="false">S2</f>
         <v>3</v>
@@ -2971,19 +3141,19 @@
       <c r="W8" s="31"/>
       <c r="X8" s="30" t="n">
         <f aca="false">V8+V10</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA8" s="30" t="n">
         <f aca="false">X8</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB8" s="31"/>
       <c r="AC8" s="30" t="n">
         <f aca="false">AA8+AA10</f>
-        <v>11</v>
-      </c>
-      <c r="AK8" s="41"/>
-      <c r="BT8" s="41"/>
+        <v>9</v>
+      </c>
+      <c r="AK8" s="40"/>
+      <c r="BT8" s="40"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
@@ -2994,40 +3164,40 @@
       </c>
       <c r="C9" s="32"/>
       <c r="D9" s="32"/>
-      <c r="E9" s="42" t="s">
+      <c r="E9" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="F9" s="42" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="43" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" s="43" t="n">
-        <v>3</v>
-      </c>
-      <c r="I9" s="44" t="n">
-        <f aca="false">((2*100%)+(100%-$I$12))/3</f>
-        <v>0.833333333333333</v>
+      <c r="I9" s="29" t="n">
+        <f aca="false">(100%+(100%-$I$12))/2</f>
+        <v>0.75</v>
       </c>
       <c r="J9" s="28" t="n">
         <f aca="false">ROUNDUP(G9/(H9*I9),0)</f>
-        <v>1</v>
-      </c>
-      <c r="P9" s="41"/>
-      <c r="U9" s="41"/>
-      <c r="V9" s="36" t="s">
+        <v>2</v>
+      </c>
+      <c r="P9" s="40"/>
+      <c r="U9" s="40"/>
+      <c r="V9" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="W9" s="36"/>
-      <c r="X9" s="36"/>
-      <c r="AA9" s="36" t="s">
+      <c r="W9" s="35"/>
+      <c r="X9" s="35"/>
+      <c r="AA9" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="AB9" s="36"/>
-      <c r="AC9" s="36"/>
-      <c r="AK9" s="41"/>
-      <c r="BT9" s="41"/>
+      <c r="AB9" s="35"/>
+      <c r="AC9" s="35"/>
+      <c r="AK9" s="40"/>
+      <c r="BT9" s="40"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
@@ -3038,63 +3208,63 @@
       </c>
       <c r="C10" s="32"/>
       <c r="D10" s="32"/>
-      <c r="E10" s="42" t="s">
+      <c r="E10" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="42" t="s">
+      <c r="F10" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="G10" s="43" t="n">
+      <c r="G10" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="43" t="n">
-        <v>3</v>
-      </c>
-      <c r="I10" s="44" t="n">
-        <f aca="false">((2*100%)+(100%-$I$12))/3</f>
-        <v>0.833333333333333</v>
+      <c r="H10" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="I10" s="29" t="n">
+        <f aca="false">(100%+(100%-$I$12))/2</f>
+        <v>0.75</v>
       </c>
       <c r="J10" s="28" t="n">
         <f aca="false">ROUNDUP(G10/(H10*I10),0)</f>
-        <v>1</v>
-      </c>
-      <c r="P10" s="41"/>
-      <c r="U10" s="39"/>
-      <c r="V10" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="P10" s="40"/>
+      <c r="U10" s="38"/>
+      <c r="V10" s="36" t="n">
         <f aca="false">J5</f>
-        <v>3</v>
-      </c>
-      <c r="W10" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="W10" s="37" t="n">
         <f aca="false">X11-X8</f>
         <v>5</v>
       </c>
-      <c r="X10" s="37" t="n">
+      <c r="X10" s="36" t="n">
         <f aca="false">AA8-X8</f>
         <v>0</v>
       </c>
-      <c r="Y10" s="39"/>
-      <c r="Z10" s="39"/>
-      <c r="AA10" s="37" t="n">
+      <c r="Y10" s="38"/>
+      <c r="Z10" s="38"/>
+      <c r="AA10" s="36" t="n">
         <f aca="false">J6</f>
-        <v>5</v>
-      </c>
-      <c r="AB10" s="38" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB10" s="37" t="n">
         <f aca="false">AC11-AC8</f>
         <v>5</v>
       </c>
-      <c r="AC10" s="37" t="n">
+      <c r="AC10" s="36" t="n">
         <f aca="false">AL2-AC8</f>
         <v>0</v>
       </c>
-      <c r="AD10" s="39"/>
-      <c r="AE10" s="39"/>
-      <c r="AF10" s="39"/>
-      <c r="AG10" s="39"/>
-      <c r="AH10" s="39"/>
-      <c r="AI10" s="39"/>
-      <c r="AJ10" s="39"/>
-      <c r="AK10" s="41"/>
-      <c r="BT10" s="41"/>
+      <c r="AD10" s="38"/>
+      <c r="AE10" s="38"/>
+      <c r="AF10" s="38"/>
+      <c r="AG10" s="38"/>
+      <c r="AH10" s="38"/>
+      <c r="AI10" s="38"/>
+      <c r="AJ10" s="38"/>
+      <c r="AK10" s="40"/>
+      <c r="BT10" s="40"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
@@ -3105,27 +3275,27 @@
       </c>
       <c r="C11" s="32"/>
       <c r="D11" s="32"/>
-      <c r="E11" s="42" t="s">
+      <c r="E11" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="F11" s="42" t="s">
+      <c r="F11" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="43" t="n">
+      <c r="G11" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="H11" s="43" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" s="44" t="n">
-        <f aca="false">((2*100%)+(100%-$I$12))/3</f>
-        <v>0.833333333333333</v>
+      <c r="H11" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="I11" s="29" t="n">
+        <f aca="false">(100%+(100%-$I$12))/2</f>
+        <v>0.75</v>
       </c>
       <c r="J11" s="28" t="n">
         <f aca="false">ROUNDUP(G11/(H11*I11),0)</f>
-        <v>1</v>
-      </c>
-      <c r="P11" s="41"/>
+        <v>2</v>
+      </c>
+      <c r="P11" s="40"/>
       <c r="V11" s="30" t="n">
         <f aca="false">X11-V10</f>
         <v>8</v>
@@ -3133,52 +3303,52 @@
       <c r="W11" s="31"/>
       <c r="X11" s="30" t="n">
         <f aca="false">AA11</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AA11" s="30" t="n">
         <f aca="false">AC11-AA10</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AB11" s="31"/>
       <c r="AC11" s="30" t="n">
         <f aca="false">AL5</f>
-        <v>16</v>
-      </c>
-      <c r="AK11" s="41"/>
-      <c r="BT11" s="41"/>
+        <v>14</v>
+      </c>
+      <c r="AK11" s="40"/>
+      <c r="BT11" s="40"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="32" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C12" s="32"/>
       <c r="D12" s="32"/>
-      <c r="E12" s="42" t="s">
+      <c r="E12" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="42" t="s">
+      <c r="F12" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="G12" s="43" t="n">
+      <c r="G12" s="42" t="n">
         <v>10</v>
       </c>
-      <c r="H12" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="44" t="n">
+      <c r="H12" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="I12" s="29" t="n">
         <v>0.5</v>
       </c>
       <c r="J12" s="28" t="n">
         <f aca="false">ROUNDUP(G12/(H12*I12),0)</f>
         <v>20</v>
       </c>
-      <c r="P12" s="41"/>
-      <c r="AA12" s="45"/>
-      <c r="AK12" s="41"/>
-      <c r="BT12" s="41"/>
+      <c r="P12" s="40"/>
+      <c r="AA12" s="43"/>
+      <c r="AK12" s="40"/>
+      <c r="BT12" s="40"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
@@ -3189,30 +3359,30 @@
       </c>
       <c r="C13" s="32"/>
       <c r="D13" s="32"/>
-      <c r="E13" s="42" t="s">
+      <c r="E13" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="F13" s="42" t="s">
+      <c r="F13" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="43" t="n">
+      <c r="G13" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="43" t="n">
-        <v>3</v>
-      </c>
-      <c r="I13" s="44" t="n">
-        <f aca="false">((2*100%)+(100%-$I$12))/3</f>
-        <v>0.833333333333333</v>
+      <c r="H13" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="I13" s="29" t="n">
+        <f aca="false">(100%+(100%-$I$12))/2</f>
+        <v>0.75</v>
       </c>
       <c r="J13" s="28" t="n">
         <f aca="false">ROUNDUP(G13/(H13*I13),0)</f>
         <v>2</v>
       </c>
-      <c r="P13" s="41"/>
-      <c r="AA13" s="45"/>
-      <c r="AK13" s="41"/>
-      <c r="BT13" s="41"/>
+      <c r="P13" s="40"/>
+      <c r="AA13" s="43"/>
+      <c r="AK13" s="40"/>
+      <c r="BT13" s="40"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
@@ -3223,27 +3393,27 @@
       </c>
       <c r="C14" s="32"/>
       <c r="D14" s="32"/>
-      <c r="E14" s="42" t="s">
+      <c r="E14" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="42" t="s">
+      <c r="F14" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="G14" s="43" t="n">
+      <c r="G14" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="H14" s="43" t="n">
-        <v>3</v>
-      </c>
-      <c r="I14" s="44" t="n">
-        <f aca="false">((2*100%)+(100%-$I$12))/3</f>
-        <v>0.833333333333333</v>
+      <c r="H14" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="I14" s="29" t="n">
+        <f aca="false">(100%+(100%-$I$12))/2</f>
+        <v>0.75</v>
       </c>
       <c r="J14" s="28" t="n">
         <f aca="false">ROUNDUP(G14/(H14*I14),0)</f>
         <v>2</v>
       </c>
-      <c r="P14" s="41"/>
+      <c r="P14" s="40"/>
       <c r="Q14" s="30" t="n">
         <f aca="false">N2</f>
         <v>2</v>
@@ -3260,19 +3430,19 @@
       <c r="W14" s="31"/>
       <c r="X14" s="30" t="n">
         <f aca="false">V14+V16</f>
-        <v>6</v>
-      </c>
-      <c r="AK14" s="41"/>
+        <v>9</v>
+      </c>
+      <c r="AK14" s="40"/>
       <c r="AL14" s="30" t="n">
         <f aca="false">X14</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AM14" s="31"/>
       <c r="AN14" s="30" t="n">
         <f aca="false">AL14+AL16</f>
-        <v>26</v>
-      </c>
-      <c r="BT14" s="41"/>
+        <v>29</v>
+      </c>
+      <c r="BT14" s="40"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
@@ -3283,56 +3453,56 @@
       </c>
       <c r="C15" s="32"/>
       <c r="D15" s="32"/>
-      <c r="E15" s="42" t="s">
+      <c r="E15" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="42" t="s">
+      <c r="F15" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="G15" s="43" t="n">
+      <c r="G15" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="43" t="n">
-        <v>3</v>
-      </c>
-      <c r="I15" s="44" t="n">
-        <f aca="false">((2*100%)+(100%-$I$12))/3</f>
-        <v>0.833333333333333</v>
+      <c r="H15" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="I15" s="29" t="n">
+        <f aca="false">(100%+(100%-$I$12))/2</f>
+        <v>0.75</v>
       </c>
       <c r="J15" s="28" t="n">
         <f aca="false">ROUNDUP(G15/(H15*I15),0)</f>
         <v>1</v>
       </c>
-      <c r="P15" s="41"/>
-      <c r="Q15" s="36" t="s">
+      <c r="P15" s="40"/>
+      <c r="Q15" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="R15" s="36"/>
-      <c r="S15" s="36"/>
-      <c r="V15" s="36" t="s">
+      <c r="R15" s="35"/>
+      <c r="S15" s="35"/>
+      <c r="V15" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="W15" s="36"/>
-      <c r="X15" s="36"/>
-      <c r="Y15" s="39"/>
-      <c r="Z15" s="39"/>
-      <c r="AA15" s="39"/>
-      <c r="AB15" s="39"/>
-      <c r="AC15" s="39"/>
-      <c r="AD15" s="39"/>
-      <c r="AE15" s="39"/>
-      <c r="AF15" s="39"/>
-      <c r="AG15" s="39"/>
-      <c r="AH15" s="39"/>
-      <c r="AI15" s="39"/>
-      <c r="AJ15" s="39"/>
-      <c r="AK15" s="45"/>
-      <c r="AL15" s="36" t="s">
+      <c r="W15" s="35"/>
+      <c r="X15" s="35"/>
+      <c r="Y15" s="38"/>
+      <c r="Z15" s="38"/>
+      <c r="AA15" s="38"/>
+      <c r="AB15" s="38"/>
+      <c r="AC15" s="38"/>
+      <c r="AD15" s="38"/>
+      <c r="AE15" s="38"/>
+      <c r="AF15" s="38"/>
+      <c r="AG15" s="38"/>
+      <c r="AH15" s="38"/>
+      <c r="AI15" s="38"/>
+      <c r="AJ15" s="38"/>
+      <c r="AK15" s="43"/>
+      <c r="AL15" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="AM15" s="36"/>
-      <c r="AN15" s="36"/>
-      <c r="BT15" s="41"/>
+      <c r="AM15" s="35"/>
+      <c r="AN15" s="35"/>
+      <c r="BT15" s="40"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
@@ -3343,130 +3513,130 @@
       </c>
       <c r="C16" s="32"/>
       <c r="D16" s="32"/>
-      <c r="E16" s="42" t="s">
+      <c r="E16" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="42" t="s">
+      <c r="F16" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="G16" s="43" t="n">
+      <c r="G16" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="H16" s="43" t="n">
-        <v>3</v>
-      </c>
-      <c r="I16" s="44" t="n">
-        <f aca="false">((2*100%)+(100%-$I$12))/3</f>
-        <v>0.833333333333333</v>
+      <c r="H16" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="I16" s="29" t="n">
+        <f aca="false">(100%+(100%-$I$12))/2</f>
+        <v>0.75</v>
       </c>
       <c r="J16" s="28" t="n">
         <f aca="false">ROUNDUP(G16/(H16*I16),0)</f>
-        <v>2</v>
-      </c>
-      <c r="P16" s="39"/>
-      <c r="Q16" s="37" t="n">
+        <v>4</v>
+      </c>
+      <c r="P16" s="38"/>
+      <c r="Q16" s="36" t="n">
         <f aca="false">J7</f>
         <v>1</v>
       </c>
-      <c r="R16" s="38" t="n">
+      <c r="R16" s="37" t="n">
         <f aca="false">S17-S14</f>
         <v>0</v>
       </c>
-      <c r="S16" s="37" t="n">
+      <c r="S16" s="36" t="n">
         <f aca="false">V14-S14</f>
         <v>0</v>
       </c>
-      <c r="T16" s="39"/>
-      <c r="U16" s="39"/>
-      <c r="V16" s="37" t="n">
+      <c r="T16" s="38"/>
+      <c r="U16" s="38"/>
+      <c r="V16" s="36" t="n">
         <f aca="false">J8</f>
-        <v>3</v>
-      </c>
-      <c r="W16" s="38" t="n">
+        <v>6</v>
+      </c>
+      <c r="W16" s="37" t="n">
         <f aca="false">X17-X14</f>
         <v>0</v>
       </c>
-      <c r="X16" s="37" t="n">
-        <f aca="false">MIN(AL14,AL2)-X14</f>
+      <c r="X16" s="36" t="n">
+        <f aca="false">MIN(AL2,AL14)-X14</f>
         <v>0</v>
       </c>
-      <c r="Y16" s="39"/>
-      <c r="Z16" s="39"/>
-      <c r="AA16" s="39"/>
-      <c r="AB16" s="39"/>
-      <c r="AC16" s="39"/>
-      <c r="AD16" s="39"/>
-      <c r="AE16" s="39"/>
-      <c r="AF16" s="39"/>
-      <c r="AG16" s="39"/>
-      <c r="AH16" s="39"/>
-      <c r="AI16" s="39"/>
-      <c r="AJ16" s="39"/>
-      <c r="AK16" s="39"/>
-      <c r="AL16" s="37" t="n">
+      <c r="Y16" s="38"/>
+      <c r="Z16" s="38"/>
+      <c r="AA16" s="38"/>
+      <c r="AB16" s="38"/>
+      <c r="AC16" s="38"/>
+      <c r="AD16" s="38"/>
+      <c r="AE16" s="38"/>
+      <c r="AF16" s="38"/>
+      <c r="AG16" s="38"/>
+      <c r="AH16" s="38"/>
+      <c r="AI16" s="38"/>
+      <c r="AJ16" s="38"/>
+      <c r="AK16" s="38"/>
+      <c r="AL16" s="36" t="n">
         <f aca="false">J12</f>
         <v>20</v>
       </c>
-      <c r="AM16" s="38" t="n">
+      <c r="AM16" s="37" t="n">
         <f aca="false">AN17-AN14</f>
         <v>0</v>
       </c>
-      <c r="AN16" s="37" t="n">
+      <c r="AN16" s="36" t="n">
         <f aca="false">BU2-AN14</f>
         <v>0</v>
       </c>
-      <c r="AO16" s="39"/>
-      <c r="AP16" s="39"/>
-      <c r="AQ16" s="39"/>
-      <c r="AR16" s="39"/>
-      <c r="AS16" s="39"/>
-      <c r="AT16" s="39"/>
-      <c r="AU16" s="39"/>
-      <c r="AV16" s="39"/>
-      <c r="AW16" s="39"/>
-      <c r="AX16" s="39"/>
-      <c r="AY16" s="39"/>
-      <c r="AZ16" s="39"/>
-      <c r="BA16" s="39"/>
-      <c r="BB16" s="39"/>
-      <c r="BC16" s="39"/>
-      <c r="BD16" s="39"/>
-      <c r="BE16" s="39"/>
-      <c r="BF16" s="39"/>
-      <c r="BG16" s="39"/>
-      <c r="BH16" s="39"/>
-      <c r="BI16" s="39"/>
-      <c r="BJ16" s="39"/>
-      <c r="BK16" s="39"/>
-      <c r="BL16" s="39"/>
-      <c r="BM16" s="39"/>
-      <c r="BN16" s="39"/>
-      <c r="BO16" s="39"/>
-      <c r="BP16" s="39"/>
-      <c r="BQ16" s="39"/>
-      <c r="BR16" s="39"/>
-      <c r="BS16" s="39"/>
+      <c r="AO16" s="38"/>
+      <c r="AP16" s="38"/>
+      <c r="AQ16" s="38"/>
+      <c r="AR16" s="38"/>
+      <c r="AS16" s="38"/>
+      <c r="AT16" s="38"/>
+      <c r="AU16" s="38"/>
+      <c r="AV16" s="38"/>
+      <c r="AW16" s="38"/>
+      <c r="AX16" s="38"/>
+      <c r="AY16" s="38"/>
+      <c r="AZ16" s="38"/>
+      <c r="BA16" s="38"/>
+      <c r="BB16" s="38"/>
+      <c r="BC16" s="38"/>
+      <c r="BD16" s="38"/>
+      <c r="BE16" s="38"/>
+      <c r="BF16" s="38"/>
+      <c r="BG16" s="38"/>
+      <c r="BH16" s="38"/>
+      <c r="BI16" s="38"/>
+      <c r="BJ16" s="38"/>
+      <c r="BK16" s="38"/>
+      <c r="BL16" s="38"/>
+      <c r="BM16" s="38"/>
+      <c r="BN16" s="38"/>
+      <c r="BO16" s="38"/>
+      <c r="BP16" s="38"/>
+      <c r="BQ16" s="38"/>
+      <c r="BR16" s="38"/>
+      <c r="BS16" s="38"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="46" t="s">
+      <c r="B17" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="46"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="47" t="s">
-        <v>57</v>
-      </c>
-      <c r="F17" s="48"/>
-      <c r="G17" s="49" t="n">
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="45" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="46"/>
+      <c r="G17" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="50" t="n">
+      <c r="H17" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="I17" s="29" t="n">
         <v>1</v>
       </c>
       <c r="J17" s="28" t="n">
@@ -3489,152 +3659,180 @@
       <c r="W17" s="31"/>
       <c r="X17" s="30" t="n">
         <f aca="false">MIN(AL5,AL17)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AL17" s="30" t="n">
         <f aca="false">AN17-AL16</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AM17" s="31"/>
       <c r="AN17" s="30" t="n">
         <f aca="false">BU5</f>
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="51" t="s">
-        <v>58</v>
-      </c>
-      <c r="B19" s="52" t="s">
-        <v>59</v>
-      </c>
-      <c r="C19" s="53"/>
-      <c r="D19" s="54" t="s">
-        <v>60</v>
+      <c r="A19" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="50"/>
+      <c r="D19" s="51" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="36" t="s">
+      <c r="B20" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="36" t="s">
+      <c r="B21" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" s="37" t="s">
+      <c r="C21" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="36" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="52" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" s="53" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="55" t="s">
+      <c r="C22" s="54"/>
+      <c r="D22" s="55" t="s">
         <v>63</v>
       </c>
-      <c r="B22" s="56" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" s="57"/>
-      <c r="D22" s="58" t="s">
-        <v>60</v>
+      <c r="G22" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I22" s="21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <f aca="false">G22/(H22*I22)</f>
+        <v>6.66666666666667</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G23" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I23" s="21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <f aca="false">G23/(H23*I23)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="59" t="s">
-        <v>64</v>
+      <c r="B24" s="56" t="s">
+        <v>67</v>
       </c>
       <c r="C24" s="31"/>
       <c r="D24" s="30" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" s="36"/>
-      <c r="D25" s="36"/>
+      <c r="B25" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="36" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="D26" s="37" t="s">
-        <v>69</v>
+      <c r="B26" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="D26" s="36" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="59" t="s">
-        <v>70</v>
+      <c r="B27" s="56" t="s">
+        <v>73</v>
       </c>
       <c r="C27" s="31"/>
       <c r="D27" s="30" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="B29" s="60" t="s">
-        <v>72</v>
-      </c>
-      <c r="C29" s="61" t="s">
-        <v>73</v>
-      </c>
-      <c r="D29" s="61"/>
+        <v>67</v>
+      </c>
+      <c r="B29" s="57" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" s="58" t="s">
+        <v>76</v>
+      </c>
+      <c r="D29" s="58"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="B30" s="60" t="s">
-        <v>72</v>
-      </c>
-      <c r="C30" s="61" t="s">
-        <v>74</v>
-      </c>
-      <c r="D30" s="61"/>
+        <v>68</v>
+      </c>
+      <c r="B30" s="57" t="s">
+        <v>75</v>
+      </c>
+      <c r="C30" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="D30" s="58"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="60"/>
+      <c r="B31" s="57"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="B32" s="60" t="s">
-        <v>72</v>
-      </c>
-      <c r="C32" s="61" t="s">
-        <v>74</v>
-      </c>
-      <c r="D32" s="61"/>
+        <v>68</v>
+      </c>
+      <c r="B32" s="57" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="D32" s="58"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="B33" s="60" t="s">
-        <v>72</v>
-      </c>
-      <c r="C33" s="61" t="s">
-        <v>73</v>
-      </c>
-      <c r="D33" s="61"/>
+        <v>67</v>
+      </c>
+      <c r="B33" s="57" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" s="58" t="s">
+        <v>76</v>
+      </c>
+      <c r="D33" s="58"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="60"/>
+      <c r="B34" s="57"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="60"/>
+      <c r="B35" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="39">
@@ -3678,7 +3876,7 @@
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="C33:D33"/>
   </mergeCells>
-  <conditionalFormatting sqref="C21 C26 V10:W10 BV4 BQ4 BL4:BM4 BG4:BH4 BB4:BC4 AW4:AX4 AR4:AS4 AM4:AN4 AM16 AB10 W16 W4 R16 R4 M4">
+  <conditionalFormatting sqref="C21 C26 W16:X16 V10:W10 AM16:AN16 BV4 BQ4 BL4 BG4 BB4 AW4 AR4 AM4 AB10 W4 R4 R16 M4">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -3690,6 +3888,1682 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
   </headerFooter>
-  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:BM22"/>
+  <sheetFormatPr defaultColWidth="11.7578125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="1"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="5" min="5" style="0" width="16.2"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="6" min="6" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11.59"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="8" min="8" style="0" width="3.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="9" style="0" width="3.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="63" min="63" style="0" width="7.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="64" style="0" width="8.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="65" min="65" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1022" style="0" width="11.52"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="40.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" s="59" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" s="59"/>
+      <c r="I1" s="60" t="n">
+        <v>44515</v>
+      </c>
+      <c r="J1" s="60" t="n">
+        <v>44516</v>
+      </c>
+      <c r="K1" s="60" t="n">
+        <v>44517</v>
+      </c>
+      <c r="L1" s="60" t="n">
+        <v>44518</v>
+      </c>
+      <c r="M1" s="60" t="n">
+        <v>44519</v>
+      </c>
+      <c r="N1" s="60" t="n">
+        <v>44520</v>
+      </c>
+      <c r="O1" s="60" t="n">
+        <v>44521</v>
+      </c>
+      <c r="P1" s="60" t="n">
+        <v>44522</v>
+      </c>
+      <c r="Q1" s="60" t="n">
+        <v>44523</v>
+      </c>
+      <c r="R1" s="60" t="n">
+        <v>44524</v>
+      </c>
+      <c r="S1" s="60" t="n">
+        <v>44525</v>
+      </c>
+      <c r="T1" s="60" t="n">
+        <v>44526</v>
+      </c>
+      <c r="U1" s="60" t="n">
+        <v>44527</v>
+      </c>
+      <c r="V1" s="60" t="n">
+        <v>44528</v>
+      </c>
+      <c r="W1" s="60" t="n">
+        <v>44529</v>
+      </c>
+      <c r="X1" s="60" t="n">
+        <v>44530</v>
+      </c>
+      <c r="Y1" s="60" t="n">
+        <v>44531</v>
+      </c>
+      <c r="Z1" s="60" t="n">
+        <v>44532</v>
+      </c>
+      <c r="AA1" s="60" t="n">
+        <v>44533</v>
+      </c>
+      <c r="AB1" s="60" t="n">
+        <v>44534</v>
+      </c>
+      <c r="AC1" s="60" t="n">
+        <v>44535</v>
+      </c>
+      <c r="AD1" s="60" t="n">
+        <v>44536</v>
+      </c>
+      <c r="AE1" s="60" t="n">
+        <v>44537</v>
+      </c>
+      <c r="AF1" s="60" t="n">
+        <v>44538</v>
+      </c>
+      <c r="AG1" s="60" t="n">
+        <v>44539</v>
+      </c>
+      <c r="AH1" s="60" t="n">
+        <v>44540</v>
+      </c>
+      <c r="AI1" s="60" t="n">
+        <v>44541</v>
+      </c>
+      <c r="AJ1" s="60" t="n">
+        <v>44542</v>
+      </c>
+      <c r="AK1" s="60" t="n">
+        <v>44543</v>
+      </c>
+      <c r="AL1" s="60" t="n">
+        <v>44544</v>
+      </c>
+      <c r="AM1" s="60" t="n">
+        <v>44545</v>
+      </c>
+      <c r="AN1" s="60" t="n">
+        <v>44546</v>
+      </c>
+      <c r="AO1" s="60" t="n">
+        <v>44547</v>
+      </c>
+      <c r="AP1" s="60" t="n">
+        <v>44548</v>
+      </c>
+      <c r="AQ1" s="60" t="n">
+        <v>44549</v>
+      </c>
+      <c r="AR1" s="60" t="n">
+        <v>44550</v>
+      </c>
+      <c r="AS1" s="60" t="n">
+        <v>44551</v>
+      </c>
+      <c r="AT1" s="60" t="n">
+        <v>44552</v>
+      </c>
+      <c r="AU1" s="60" t="n">
+        <v>44553</v>
+      </c>
+      <c r="AV1" s="61" t="n">
+        <v>44554</v>
+      </c>
+      <c r="AW1" s="60" t="n">
+        <v>44555</v>
+      </c>
+      <c r="AX1" s="60" t="n">
+        <v>44556</v>
+      </c>
+      <c r="AY1" s="60" t="n">
+        <v>44557</v>
+      </c>
+      <c r="AZ1" s="60" t="n">
+        <v>44558</v>
+      </c>
+      <c r="BA1" s="60" t="n">
+        <v>44559</v>
+      </c>
+      <c r="BB1" s="60" t="n">
+        <v>44560</v>
+      </c>
+      <c r="BC1" s="61" t="n">
+        <v>44561</v>
+      </c>
+      <c r="BD1" s="60" t="n">
+        <v>44562</v>
+      </c>
+      <c r="BE1" s="60" t="n">
+        <v>44563</v>
+      </c>
+      <c r="BF1" s="60" t="n">
+        <v>44564</v>
+      </c>
+      <c r="BG1" s="60" t="n">
+        <v>44565</v>
+      </c>
+      <c r="BH1" s="60" t="n">
+        <v>44566</v>
+      </c>
+      <c r="BI1" s="61" t="n">
+        <v>44567</v>
+      </c>
+      <c r="BJ1" s="60" t="n">
+        <v>44568</v>
+      </c>
+      <c r="BK1" s="62"/>
+      <c r="BL1" s="63"/>
+      <c r="BM1" s="64"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2" s="65" t="n">
+        <f aca="false">Netzplan!J2</f>
+        <v>2</v>
+      </c>
+      <c r="H2" s="66" t="n">
+        <f aca="false">SUM(I2:BJ2)</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="68"/>
+      <c r="O2" s="68"/>
+      <c r="P2" s="68"/>
+      <c r="Q2" s="68"/>
+      <c r="R2" s="68"/>
+      <c r="S2" s="68"/>
+      <c r="T2" s="68"/>
+      <c r="U2" s="68"/>
+      <c r="V2" s="68"/>
+      <c r="W2" s="68"/>
+      <c r="X2" s="68"/>
+      <c r="Y2" s="68"/>
+      <c r="Z2" s="68"/>
+      <c r="AA2" s="68"/>
+      <c r="AB2" s="68"/>
+      <c r="AC2" s="68"/>
+      <c r="AD2" s="68"/>
+      <c r="AE2" s="68"/>
+      <c r="AF2" s="68"/>
+      <c r="AG2" s="68"/>
+      <c r="AH2" s="68"/>
+      <c r="AI2" s="68"/>
+      <c r="AJ2" s="68"/>
+      <c r="AK2" s="68"/>
+      <c r="AL2" s="68"/>
+      <c r="AM2" s="68"/>
+      <c r="AN2" s="68"/>
+      <c r="AO2" s="68"/>
+      <c r="AP2" s="68"/>
+      <c r="AQ2" s="68"/>
+      <c r="AR2" s="68"/>
+      <c r="AS2" s="68"/>
+      <c r="AT2" s="68"/>
+      <c r="AU2" s="68"/>
+      <c r="AV2" s="69"/>
+      <c r="AW2" s="68"/>
+      <c r="AX2" s="68"/>
+      <c r="AY2" s="68"/>
+      <c r="AZ2" s="68"/>
+      <c r="BA2" s="68"/>
+      <c r="BB2" s="68"/>
+      <c r="BC2" s="69"/>
+      <c r="BD2" s="68"/>
+      <c r="BE2" s="68"/>
+      <c r="BF2" s="68"/>
+      <c r="BG2" s="68"/>
+      <c r="BH2" s="68"/>
+      <c r="BI2" s="69"/>
+      <c r="BJ2" s="70"/>
+      <c r="BK2" s="62"/>
+      <c r="BL2" s="63"/>
+      <c r="BM2" s="64"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" s="65" t="n">
+        <f aca="false">Netzplan!J3</f>
+        <v>1</v>
+      </c>
+      <c r="H3" s="66" t="n">
+        <f aca="false">SUM(I3:BJ3)</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
+      <c r="M3" s="71"/>
+      <c r="N3" s="71"/>
+      <c r="O3" s="71"/>
+      <c r="P3" s="72"/>
+      <c r="Q3" s="71"/>
+      <c r="R3" s="71"/>
+      <c r="S3" s="71"/>
+      <c r="T3" s="71"/>
+      <c r="U3" s="71"/>
+      <c r="V3" s="71"/>
+      <c r="W3" s="71"/>
+      <c r="X3" s="71"/>
+      <c r="Y3" s="71"/>
+      <c r="Z3" s="71"/>
+      <c r="AA3" s="71"/>
+      <c r="AB3" s="71"/>
+      <c r="AC3" s="71"/>
+      <c r="AD3" s="71"/>
+      <c r="AE3" s="71"/>
+      <c r="AF3" s="71"/>
+      <c r="AG3" s="71"/>
+      <c r="AH3" s="71"/>
+      <c r="AI3" s="71"/>
+      <c r="AJ3" s="71"/>
+      <c r="AK3" s="71"/>
+      <c r="AL3" s="71"/>
+      <c r="AM3" s="71"/>
+      <c r="AN3" s="71"/>
+      <c r="AO3" s="71"/>
+      <c r="AP3" s="71"/>
+      <c r="AQ3" s="71"/>
+      <c r="AR3" s="71"/>
+      <c r="AS3" s="71"/>
+      <c r="AT3" s="71"/>
+      <c r="AU3" s="71"/>
+      <c r="AV3" s="73"/>
+      <c r="AW3" s="71"/>
+      <c r="AX3" s="71"/>
+      <c r="AY3" s="71"/>
+      <c r="AZ3" s="71"/>
+      <c r="BA3" s="71"/>
+      <c r="BB3" s="71"/>
+      <c r="BC3" s="73"/>
+      <c r="BD3" s="71"/>
+      <c r="BE3" s="71"/>
+      <c r="BF3" s="71"/>
+      <c r="BG3" s="71"/>
+      <c r="BH3" s="71"/>
+      <c r="BI3" s="73"/>
+      <c r="BJ3" s="74"/>
+      <c r="BK3" s="62"/>
+      <c r="BL3" s="63"/>
+      <c r="BM3" s="64"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="65" t="n">
+        <f aca="false">Netzplan!J4</f>
+        <v>6</v>
+      </c>
+      <c r="H4" s="66" t="n">
+        <f aca="false">SUM(I4:BJ4)</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="71"/>
+      <c r="J4" s="71"/>
+      <c r="K4" s="71"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="71"/>
+      <c r="N4" s="71"/>
+      <c r="O4" s="71"/>
+      <c r="P4" s="71"/>
+      <c r="Q4" s="72"/>
+      <c r="R4" s="72"/>
+      <c r="S4" s="72"/>
+      <c r="T4" s="72"/>
+      <c r="U4" s="71"/>
+      <c r="V4" s="71"/>
+      <c r="W4" s="71"/>
+      <c r="X4" s="71"/>
+      <c r="Y4" s="71"/>
+      <c r="Z4" s="71"/>
+      <c r="AA4" s="71"/>
+      <c r="AB4" s="71"/>
+      <c r="AC4" s="71"/>
+      <c r="AD4" s="71"/>
+      <c r="AE4" s="71"/>
+      <c r="AF4" s="71"/>
+      <c r="AG4" s="71"/>
+      <c r="AH4" s="71"/>
+      <c r="AI4" s="71"/>
+      <c r="AJ4" s="71"/>
+      <c r="AK4" s="71"/>
+      <c r="AL4" s="71"/>
+      <c r="AM4" s="71"/>
+      <c r="AN4" s="71"/>
+      <c r="AO4" s="71"/>
+      <c r="AP4" s="71"/>
+      <c r="AQ4" s="71"/>
+      <c r="AR4" s="71"/>
+      <c r="AS4" s="71"/>
+      <c r="AT4" s="71"/>
+      <c r="AU4" s="71"/>
+      <c r="AV4" s="73"/>
+      <c r="AW4" s="71"/>
+      <c r="AX4" s="71"/>
+      <c r="AY4" s="71"/>
+      <c r="AZ4" s="71"/>
+      <c r="BA4" s="71"/>
+      <c r="BB4" s="71"/>
+      <c r="BC4" s="73"/>
+      <c r="BD4" s="71"/>
+      <c r="BE4" s="71"/>
+      <c r="BF4" s="71"/>
+      <c r="BG4" s="71"/>
+      <c r="BH4" s="71"/>
+      <c r="BI4" s="73"/>
+      <c r="BJ4" s="74"/>
+      <c r="BK4" s="62"/>
+      <c r="BL4" s="63"/>
+      <c r="BM4" s="64"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="65" t="n">
+        <f aca="false">Netzplan!J5</f>
+        <v>2</v>
+      </c>
+      <c r="H5" s="66" t="n">
+        <f aca="false">SUM(I5:BJ5)</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="71"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="71"/>
+      <c r="L5" s="72"/>
+      <c r="M5" s="72"/>
+      <c r="N5" s="71"/>
+      <c r="O5" s="71"/>
+      <c r="P5" s="71"/>
+      <c r="Q5" s="72"/>
+      <c r="R5" s="72"/>
+      <c r="S5" s="75"/>
+      <c r="T5" s="71"/>
+      <c r="U5" s="71"/>
+      <c r="V5" s="71"/>
+      <c r="W5" s="71"/>
+      <c r="X5" s="71"/>
+      <c r="Y5" s="71"/>
+      <c r="Z5" s="71"/>
+      <c r="AA5" s="71"/>
+      <c r="AB5" s="71"/>
+      <c r="AC5" s="71"/>
+      <c r="AD5" s="71"/>
+      <c r="AE5" s="71"/>
+      <c r="AF5" s="71"/>
+      <c r="AG5" s="71"/>
+      <c r="AH5" s="71"/>
+      <c r="AI5" s="71"/>
+      <c r="AJ5" s="71"/>
+      <c r="AK5" s="71"/>
+      <c r="AL5" s="71"/>
+      <c r="AM5" s="71"/>
+      <c r="AN5" s="71"/>
+      <c r="AO5" s="71"/>
+      <c r="AP5" s="71"/>
+      <c r="AQ5" s="71"/>
+      <c r="AR5" s="71"/>
+      <c r="AS5" s="71"/>
+      <c r="AT5" s="71"/>
+      <c r="AU5" s="71"/>
+      <c r="AV5" s="73"/>
+      <c r="AW5" s="71"/>
+      <c r="AX5" s="71"/>
+      <c r="AY5" s="71"/>
+      <c r="AZ5" s="71"/>
+      <c r="BA5" s="71"/>
+      <c r="BB5" s="71"/>
+      <c r="BC5" s="73"/>
+      <c r="BD5" s="71"/>
+      <c r="BE5" s="71"/>
+      <c r="BF5" s="71"/>
+      <c r="BG5" s="71"/>
+      <c r="BH5" s="71"/>
+      <c r="BI5" s="73"/>
+      <c r="BJ5" s="74"/>
+      <c r="BK5" s="62"/>
+      <c r="BL5" s="63"/>
+      <c r="BM5" s="64"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="41" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="65" t="n">
+        <f aca="false">Netzplan!J6</f>
+        <v>4</v>
+      </c>
+      <c r="H6" s="66" t="n">
+        <f aca="false">SUM(I6:BJ6)</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="71"/>
+      <c r="L6" s="71"/>
+      <c r="M6" s="71"/>
+      <c r="N6" s="71"/>
+      <c r="O6" s="71"/>
+      <c r="P6" s="72"/>
+      <c r="Q6" s="72"/>
+      <c r="R6" s="72"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="71"/>
+      <c r="V6" s="71"/>
+      <c r="W6" s="72"/>
+      <c r="X6" s="72"/>
+      <c r="Y6" s="72"/>
+      <c r="Z6" s="72"/>
+      <c r="AA6" s="75"/>
+      <c r="AB6" s="71"/>
+      <c r="AC6" s="71"/>
+      <c r="AD6" s="71"/>
+      <c r="AE6" s="71"/>
+      <c r="AF6" s="71"/>
+      <c r="AG6" s="71"/>
+      <c r="AH6" s="71"/>
+      <c r="AI6" s="71"/>
+      <c r="AJ6" s="71"/>
+      <c r="AK6" s="71"/>
+      <c r="AL6" s="71"/>
+      <c r="AM6" s="71"/>
+      <c r="AN6" s="71"/>
+      <c r="AO6" s="71"/>
+      <c r="AP6" s="71"/>
+      <c r="AQ6" s="71"/>
+      <c r="AR6" s="71"/>
+      <c r="AS6" s="71"/>
+      <c r="AT6" s="71"/>
+      <c r="AU6" s="71"/>
+      <c r="AV6" s="73"/>
+      <c r="AW6" s="71"/>
+      <c r="AX6" s="71"/>
+      <c r="AY6" s="71"/>
+      <c r="AZ6" s="71"/>
+      <c r="BA6" s="71"/>
+      <c r="BB6" s="71"/>
+      <c r="BC6" s="73"/>
+      <c r="BD6" s="71"/>
+      <c r="BE6" s="71"/>
+      <c r="BF6" s="71"/>
+      <c r="BG6" s="71"/>
+      <c r="BH6" s="71"/>
+      <c r="BI6" s="73"/>
+      <c r="BJ6" s="74"/>
+      <c r="BK6" s="62"/>
+      <c r="BL6" s="63"/>
+      <c r="BM6" s="64"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="65" t="n">
+        <f aca="false">Netzplan!J7</f>
+        <v>1</v>
+      </c>
+      <c r="H7" s="66" t="n">
+        <f aca="false">SUM(I7:BJ7)</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="71"/>
+      <c r="J7" s="71"/>
+      <c r="K7" s="71"/>
+      <c r="L7" s="71"/>
+      <c r="M7" s="71"/>
+      <c r="N7" s="71"/>
+      <c r="O7" s="71"/>
+      <c r="P7" s="72"/>
+      <c r="Q7" s="71"/>
+      <c r="R7" s="71"/>
+      <c r="S7" s="71"/>
+      <c r="T7" s="71"/>
+      <c r="U7" s="71"/>
+      <c r="V7" s="71"/>
+      <c r="W7" s="71"/>
+      <c r="X7" s="71"/>
+      <c r="Y7" s="71"/>
+      <c r="Z7" s="71"/>
+      <c r="AA7" s="71"/>
+      <c r="AB7" s="71"/>
+      <c r="AC7" s="71"/>
+      <c r="AD7" s="71"/>
+      <c r="AE7" s="71"/>
+      <c r="AF7" s="71"/>
+      <c r="AG7" s="71"/>
+      <c r="AH7" s="71"/>
+      <c r="AI7" s="71"/>
+      <c r="AJ7" s="71"/>
+      <c r="AK7" s="71"/>
+      <c r="AL7" s="71"/>
+      <c r="AM7" s="71"/>
+      <c r="AN7" s="71"/>
+      <c r="AO7" s="71"/>
+      <c r="AP7" s="71"/>
+      <c r="AQ7" s="71"/>
+      <c r="AR7" s="71"/>
+      <c r="AS7" s="71"/>
+      <c r="AT7" s="71"/>
+      <c r="AU7" s="71"/>
+      <c r="AV7" s="73"/>
+      <c r="AW7" s="71"/>
+      <c r="AX7" s="71"/>
+      <c r="AY7" s="71"/>
+      <c r="AZ7" s="71"/>
+      <c r="BA7" s="71"/>
+      <c r="BB7" s="71"/>
+      <c r="BC7" s="73"/>
+      <c r="BD7" s="71"/>
+      <c r="BE7" s="71"/>
+      <c r="BF7" s="71"/>
+      <c r="BG7" s="71"/>
+      <c r="BH7" s="71"/>
+      <c r="BI7" s="73"/>
+      <c r="BJ7" s="74"/>
+      <c r="BK7" s="62"/>
+      <c r="BL7" s="63"/>
+      <c r="BM7" s="64"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="65" t="n">
+        <f aca="false">Netzplan!J8</f>
+        <v>6</v>
+      </c>
+      <c r="H8" s="66" t="n">
+        <f aca="false">SUM(I8:BJ8)</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="71"/>
+      <c r="J8" s="71"/>
+      <c r="K8" s="71"/>
+      <c r="L8" s="72"/>
+      <c r="M8" s="72"/>
+      <c r="N8" s="71"/>
+      <c r="O8" s="71"/>
+      <c r="P8" s="72"/>
+      <c r="Q8" s="72"/>
+      <c r="R8" s="72"/>
+      <c r="S8" s="72"/>
+      <c r="T8" s="71"/>
+      <c r="U8" s="71"/>
+      <c r="V8" s="71"/>
+      <c r="W8" s="71"/>
+      <c r="X8" s="71"/>
+      <c r="Y8" s="71"/>
+      <c r="Z8" s="71"/>
+      <c r="AA8" s="71"/>
+      <c r="AB8" s="71"/>
+      <c r="AC8" s="71"/>
+      <c r="AD8" s="71"/>
+      <c r="AE8" s="71"/>
+      <c r="AF8" s="71"/>
+      <c r="AG8" s="71"/>
+      <c r="AH8" s="71"/>
+      <c r="AI8" s="71"/>
+      <c r="AJ8" s="71"/>
+      <c r="AK8" s="71"/>
+      <c r="AL8" s="71"/>
+      <c r="AM8" s="71"/>
+      <c r="AN8" s="71"/>
+      <c r="AO8" s="71"/>
+      <c r="AP8" s="71"/>
+      <c r="AQ8" s="71"/>
+      <c r="AR8" s="71"/>
+      <c r="AS8" s="71"/>
+      <c r="AT8" s="71"/>
+      <c r="AU8" s="71"/>
+      <c r="AV8" s="73"/>
+      <c r="AW8" s="71"/>
+      <c r="AX8" s="71"/>
+      <c r="AY8" s="71"/>
+      <c r="AZ8" s="71"/>
+      <c r="BA8" s="71"/>
+      <c r="BB8" s="71"/>
+      <c r="BC8" s="73"/>
+      <c r="BD8" s="71"/>
+      <c r="BE8" s="71"/>
+      <c r="BF8" s="71"/>
+      <c r="BG8" s="71"/>
+      <c r="BH8" s="71"/>
+      <c r="BI8" s="73"/>
+      <c r="BJ8" s="74"/>
+      <c r="BK8" s="62"/>
+      <c r="BL8" s="63"/>
+      <c r="BM8" s="64"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14"/>
+      <c r="B9" s="42" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="65"/>
+      <c r="H9" s="66"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="71"/>
+      <c r="L9" s="72"/>
+      <c r="M9" s="72"/>
+      <c r="N9" s="71"/>
+      <c r="O9" s="71"/>
+      <c r="P9" s="72"/>
+      <c r="Q9" s="72"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="72"/>
+      <c r="T9" s="71"/>
+      <c r="U9" s="71"/>
+      <c r="V9" s="71"/>
+      <c r="W9" s="71"/>
+      <c r="X9" s="71"/>
+      <c r="Y9" s="71"/>
+      <c r="Z9" s="71"/>
+      <c r="AA9" s="71"/>
+      <c r="AB9" s="71"/>
+      <c r="AC9" s="71"/>
+      <c r="AD9" s="71"/>
+      <c r="AE9" s="71"/>
+      <c r="AF9" s="71"/>
+      <c r="AG9" s="71"/>
+      <c r="AH9" s="71"/>
+      <c r="AI9" s="71"/>
+      <c r="AJ9" s="71"/>
+      <c r="AK9" s="71"/>
+      <c r="AL9" s="71"/>
+      <c r="AM9" s="71"/>
+      <c r="AN9" s="71"/>
+      <c r="AO9" s="71"/>
+      <c r="AP9" s="71"/>
+      <c r="AQ9" s="71"/>
+      <c r="AR9" s="71"/>
+      <c r="AS9" s="71"/>
+      <c r="AT9" s="71"/>
+      <c r="AU9" s="71"/>
+      <c r="AV9" s="73"/>
+      <c r="AW9" s="71"/>
+      <c r="AX9" s="71"/>
+      <c r="AY9" s="71"/>
+      <c r="AZ9" s="71"/>
+      <c r="BA9" s="71"/>
+      <c r="BB9" s="71"/>
+      <c r="BC9" s="73"/>
+      <c r="BD9" s="71"/>
+      <c r="BE9" s="71"/>
+      <c r="BF9" s="71"/>
+      <c r="BG9" s="71"/>
+      <c r="BH9" s="71"/>
+      <c r="BI9" s="73"/>
+      <c r="BJ9" s="74"/>
+      <c r="BK9" s="62"/>
+      <c r="BL9" s="63"/>
+      <c r="BM9" s="64"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="65" t="n">
+        <f aca="false">Netzplan!J9</f>
+        <v>2</v>
+      </c>
+      <c r="H10" s="66" t="n">
+        <f aca="false">SUM(I10:BJ10)</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="71"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="71"/>
+      <c r="L10" s="71"/>
+      <c r="M10" s="71"/>
+      <c r="N10" s="71"/>
+      <c r="O10" s="71"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="71"/>
+      <c r="S10" s="71"/>
+      <c r="T10" s="72"/>
+      <c r="U10" s="71"/>
+      <c r="V10" s="71"/>
+      <c r="W10" s="72"/>
+      <c r="X10" s="72"/>
+      <c r="Y10" s="72"/>
+      <c r="Z10" s="72"/>
+      <c r="AA10" s="74"/>
+      <c r="AB10" s="71"/>
+      <c r="AC10" s="71"/>
+      <c r="AD10" s="72"/>
+      <c r="AE10" s="71"/>
+      <c r="AF10" s="71"/>
+      <c r="AG10" s="71"/>
+      <c r="AH10" s="71"/>
+      <c r="AI10" s="71"/>
+      <c r="AJ10" s="71"/>
+      <c r="AK10" s="71"/>
+      <c r="AL10" s="71"/>
+      <c r="AM10" s="71"/>
+      <c r="AN10" s="71"/>
+      <c r="AO10" s="71"/>
+      <c r="AP10" s="71"/>
+      <c r="AQ10" s="71"/>
+      <c r="AR10" s="71"/>
+      <c r="AS10" s="71"/>
+      <c r="AT10" s="71"/>
+      <c r="AU10" s="71"/>
+      <c r="AV10" s="73"/>
+      <c r="AW10" s="71"/>
+      <c r="AX10" s="71"/>
+      <c r="AY10" s="71"/>
+      <c r="AZ10" s="71"/>
+      <c r="BA10" s="71"/>
+      <c r="BB10" s="71"/>
+      <c r="BC10" s="73"/>
+      <c r="BD10" s="71"/>
+      <c r="BE10" s="71"/>
+      <c r="BF10" s="71"/>
+      <c r="BG10" s="71"/>
+      <c r="BH10" s="71"/>
+      <c r="BI10" s="73"/>
+      <c r="BJ10" s="74"/>
+      <c r="BK10" s="62"/>
+      <c r="BL10" s="63"/>
+      <c r="BM10" s="64"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="41" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="65" t="n">
+        <f aca="false">Netzplan!J10</f>
+        <v>2</v>
+      </c>
+      <c r="H11" s="66" t="n">
+        <f aca="false">SUM(I11:BJ11)</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="71"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="71"/>
+      <c r="L11" s="71"/>
+      <c r="M11" s="71"/>
+      <c r="N11" s="71"/>
+      <c r="O11" s="71"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="71"/>
+      <c r="S11" s="71"/>
+      <c r="T11" s="71"/>
+      <c r="U11" s="71"/>
+      <c r="V11" s="71"/>
+      <c r="W11" s="71"/>
+      <c r="X11" s="72"/>
+      <c r="Y11" s="72"/>
+      <c r="Z11" s="71"/>
+      <c r="AA11" s="71"/>
+      <c r="AB11" s="71"/>
+      <c r="AC11" s="71"/>
+      <c r="AE11" s="74"/>
+      <c r="AF11" s="71"/>
+      <c r="AG11" s="71"/>
+      <c r="AH11" s="71"/>
+      <c r="AI11" s="71"/>
+      <c r="AJ11" s="71"/>
+      <c r="AK11" s="71"/>
+      <c r="AL11" s="71"/>
+      <c r="AM11" s="71"/>
+      <c r="AN11" s="71"/>
+      <c r="AO11" s="71"/>
+      <c r="AP11" s="71"/>
+      <c r="AQ11" s="71"/>
+      <c r="AR11" s="71"/>
+      <c r="AS11" s="71"/>
+      <c r="AT11" s="71"/>
+      <c r="AU11" s="71"/>
+      <c r="AV11" s="73"/>
+      <c r="AW11" s="71"/>
+      <c r="AX11" s="71"/>
+      <c r="AY11" s="71"/>
+      <c r="AZ11" s="71"/>
+      <c r="BA11" s="71"/>
+      <c r="BB11" s="71"/>
+      <c r="BC11" s="73"/>
+      <c r="BD11" s="71"/>
+      <c r="BE11" s="71"/>
+      <c r="BF11" s="71"/>
+      <c r="BG11" s="71"/>
+      <c r="BH11" s="71"/>
+      <c r="BI11" s="73"/>
+      <c r="BJ11" s="74"/>
+      <c r="BK11" s="62"/>
+      <c r="BL11" s="63"/>
+      <c r="BM11" s="64"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="65" t="n">
+        <f aca="false">Netzplan!J11</f>
+        <v>2</v>
+      </c>
+      <c r="H12" s="66" t="n">
+        <f aca="false">SUM(I12:BJ12)</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="71"/>
+      <c r="J12" s="71"/>
+      <c r="K12" s="71"/>
+      <c r="L12" s="71"/>
+      <c r="M12" s="71"/>
+      <c r="N12" s="71"/>
+      <c r="O12" s="71"/>
+      <c r="P12" s="71"/>
+      <c r="Q12" s="71"/>
+      <c r="R12" s="71"/>
+      <c r="S12" s="71"/>
+      <c r="T12" s="71"/>
+      <c r="U12" s="71"/>
+      <c r="V12" s="71"/>
+      <c r="W12" s="71"/>
+      <c r="X12" s="71"/>
+      <c r="Y12" s="71"/>
+      <c r="Z12" s="72"/>
+      <c r="AA12" s="72"/>
+      <c r="AB12" s="71"/>
+      <c r="AC12" s="71"/>
+      <c r="AE12" s="74"/>
+      <c r="AF12" s="71"/>
+      <c r="AG12" s="72"/>
+      <c r="AH12" s="72"/>
+      <c r="AI12" s="71"/>
+      <c r="AJ12" s="71"/>
+      <c r="AK12" s="71"/>
+      <c r="AL12" s="71"/>
+      <c r="AM12" s="71"/>
+      <c r="AN12" s="71"/>
+      <c r="AO12" s="71"/>
+      <c r="AP12" s="71"/>
+      <c r="AQ12" s="71"/>
+      <c r="AR12" s="71"/>
+      <c r="AS12" s="71"/>
+      <c r="AT12" s="71"/>
+      <c r="AU12" s="71"/>
+      <c r="AV12" s="73"/>
+      <c r="AW12" s="71"/>
+      <c r="AX12" s="71"/>
+      <c r="AY12" s="71"/>
+      <c r="AZ12" s="71"/>
+      <c r="BA12" s="71"/>
+      <c r="BB12" s="71"/>
+      <c r="BC12" s="73"/>
+      <c r="BD12" s="71"/>
+      <c r="BE12" s="71"/>
+      <c r="BF12" s="71"/>
+      <c r="BG12" s="71"/>
+      <c r="BH12" s="71"/>
+      <c r="BI12" s="73"/>
+      <c r="BJ12" s="74"/>
+      <c r="BK12" s="62"/>
+      <c r="BL12" s="63"/>
+      <c r="BM12" s="64"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="65" t="n">
+        <f aca="false">Netzplan!J12</f>
+        <v>20</v>
+      </c>
+      <c r="H13" s="66" t="n">
+        <f aca="false">SUM(I13:BJ13)</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="71"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="71"/>
+      <c r="L13" s="71"/>
+      <c r="M13" s="71"/>
+      <c r="N13" s="71"/>
+      <c r="O13" s="71"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="71"/>
+      <c r="S13" s="71"/>
+      <c r="T13" s="72"/>
+      <c r="U13" s="71"/>
+      <c r="V13" s="71"/>
+      <c r="W13" s="72"/>
+      <c r="X13" s="72"/>
+      <c r="Y13" s="72"/>
+      <c r="Z13" s="72"/>
+      <c r="AA13" s="72"/>
+      <c r="AB13" s="71"/>
+      <c r="AC13" s="71"/>
+      <c r="AD13" s="72"/>
+      <c r="AE13" s="72"/>
+      <c r="AF13" s="72"/>
+      <c r="AG13" s="72"/>
+      <c r="AH13" s="72"/>
+      <c r="AI13" s="71"/>
+      <c r="AJ13" s="71"/>
+      <c r="AK13" s="72"/>
+      <c r="AL13" s="72"/>
+      <c r="AM13" s="72"/>
+      <c r="AN13" s="72"/>
+      <c r="AO13" s="72"/>
+      <c r="AP13" s="71"/>
+      <c r="AQ13" s="71"/>
+      <c r="AR13" s="72"/>
+      <c r="AS13" s="72"/>
+      <c r="AT13" s="72"/>
+      <c r="AU13" s="72"/>
+      <c r="AV13" s="76"/>
+      <c r="AW13" s="71"/>
+      <c r="AX13" s="71"/>
+      <c r="AY13" s="72"/>
+      <c r="AZ13" s="72"/>
+      <c r="BA13" s="72"/>
+      <c r="BB13" s="72"/>
+      <c r="BC13" s="73"/>
+      <c r="BD13" s="71"/>
+      <c r="BE13" s="71"/>
+      <c r="BF13" s="71"/>
+      <c r="BG13" s="71"/>
+      <c r="BH13" s="71"/>
+      <c r="BI13" s="73"/>
+      <c r="BJ13" s="74"/>
+      <c r="BK13" s="62"/>
+      <c r="BL13" s="63"/>
+      <c r="BM13" s="64"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="14"/>
+      <c r="B14" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="71"/>
+      <c r="L14" s="71"/>
+      <c r="M14" s="71"/>
+      <c r="N14" s="71"/>
+      <c r="O14" s="71"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="71"/>
+      <c r="S14" s="71"/>
+      <c r="T14" s="72"/>
+      <c r="U14" s="71"/>
+      <c r="V14" s="71"/>
+      <c r="W14" s="72"/>
+      <c r="X14" s="72"/>
+      <c r="Y14" s="72"/>
+      <c r="Z14" s="72"/>
+      <c r="AA14" s="72"/>
+      <c r="AB14" s="71"/>
+      <c r="AC14" s="71"/>
+      <c r="AD14" s="72"/>
+      <c r="AE14" s="72"/>
+      <c r="AF14" s="72"/>
+      <c r="AG14" s="72"/>
+      <c r="AH14" s="72"/>
+      <c r="AI14" s="71"/>
+      <c r="AJ14" s="71"/>
+      <c r="AK14" s="72"/>
+      <c r="AL14" s="72"/>
+      <c r="AM14" s="72"/>
+      <c r="AN14" s="72"/>
+      <c r="AO14" s="72"/>
+      <c r="AP14" s="71"/>
+      <c r="AQ14" s="71"/>
+      <c r="AR14" s="72"/>
+      <c r="AS14" s="72"/>
+      <c r="AT14" s="72"/>
+      <c r="AU14" s="72"/>
+      <c r="AV14" s="76"/>
+      <c r="AW14" s="71"/>
+      <c r="AX14" s="71"/>
+      <c r="AY14" s="72"/>
+      <c r="AZ14" s="72"/>
+      <c r="BA14" s="72"/>
+      <c r="BB14" s="72"/>
+      <c r="BC14" s="73"/>
+      <c r="BD14" s="71"/>
+      <c r="BE14" s="71"/>
+      <c r="BF14" s="71"/>
+      <c r="BG14" s="71"/>
+      <c r="BH14" s="71"/>
+      <c r="BI14" s="73"/>
+      <c r="BJ14" s="74"/>
+      <c r="BK14" s="62"/>
+      <c r="BL14" s="63"/>
+      <c r="BM14" s="64"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15" s="65" t="n">
+        <f aca="false">Netzplan!J13</f>
+        <v>2</v>
+      </c>
+      <c r="H15" s="66" t="n">
+        <f aca="false">SUM(I15:BJ15)</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="71"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="71"/>
+      <c r="L15" s="71"/>
+      <c r="M15" s="71"/>
+      <c r="N15" s="71"/>
+      <c r="O15" s="71"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="71"/>
+      <c r="S15" s="71"/>
+      <c r="T15" s="71"/>
+      <c r="U15" s="71"/>
+      <c r="V15" s="71"/>
+      <c r="W15" s="71"/>
+      <c r="X15" s="71"/>
+      <c r="Y15" s="71"/>
+      <c r="Z15" s="71"/>
+      <c r="AA15" s="71"/>
+      <c r="AB15" s="71"/>
+      <c r="AC15" s="71"/>
+      <c r="AE15" s="72"/>
+      <c r="AF15" s="72"/>
+      <c r="AG15" s="71"/>
+      <c r="AH15" s="71"/>
+      <c r="AI15" s="71"/>
+      <c r="AJ15" s="71"/>
+      <c r="AK15" s="72"/>
+      <c r="AL15" s="72"/>
+      <c r="AM15" s="72"/>
+      <c r="AN15" s="72"/>
+      <c r="AO15" s="72"/>
+      <c r="AP15" s="71"/>
+      <c r="AQ15" s="71"/>
+      <c r="AR15" s="71"/>
+      <c r="AS15" s="71"/>
+      <c r="AT15" s="71"/>
+      <c r="AU15" s="71"/>
+      <c r="AV15" s="73"/>
+      <c r="AW15" s="71"/>
+      <c r="AX15" s="71"/>
+      <c r="AY15" s="71"/>
+      <c r="AZ15" s="71"/>
+      <c r="BA15" s="71"/>
+      <c r="BB15" s="71"/>
+      <c r="BC15" s="73"/>
+      <c r="BD15" s="71"/>
+      <c r="BE15" s="71"/>
+      <c r="BF15" s="71"/>
+      <c r="BG15" s="71"/>
+      <c r="BH15" s="71"/>
+      <c r="BI15" s="73"/>
+      <c r="BJ15" s="74"/>
+      <c r="BK15" s="62"/>
+      <c r="BL15" s="63"/>
+      <c r="BM15" s="64"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="65" t="n">
+        <f aca="false">Netzplan!J14</f>
+        <v>2</v>
+      </c>
+      <c r="H16" s="66" t="n">
+        <f aca="false">SUM(I16:BJ16)</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="71"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="71"/>
+      <c r="L16" s="71"/>
+      <c r="M16" s="71"/>
+      <c r="N16" s="71"/>
+      <c r="O16" s="71"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="71"/>
+      <c r="S16" s="71"/>
+      <c r="T16" s="71"/>
+      <c r="U16" s="71"/>
+      <c r="V16" s="71"/>
+      <c r="W16" s="71"/>
+      <c r="X16" s="71"/>
+      <c r="Y16" s="71"/>
+      <c r="Z16" s="71"/>
+      <c r="AA16" s="71"/>
+      <c r="AB16" s="71"/>
+      <c r="AC16" s="71"/>
+      <c r="AD16" s="71"/>
+      <c r="AE16" s="71"/>
+      <c r="AG16" s="71"/>
+      <c r="AH16" s="71"/>
+      <c r="AI16" s="71"/>
+      <c r="AJ16" s="71"/>
+      <c r="AL16" s="71"/>
+      <c r="AM16" s="71"/>
+      <c r="AN16" s="71"/>
+      <c r="AO16" s="72"/>
+      <c r="AP16" s="71"/>
+      <c r="AQ16" s="71"/>
+      <c r="AR16" s="72"/>
+      <c r="AS16" s="72"/>
+      <c r="AT16" s="72"/>
+      <c r="AU16" s="71"/>
+      <c r="AV16" s="73"/>
+      <c r="AW16" s="71"/>
+      <c r="AX16" s="71"/>
+      <c r="AY16" s="71"/>
+      <c r="AZ16" s="71"/>
+      <c r="BA16" s="71"/>
+      <c r="BB16" s="71"/>
+      <c r="BC16" s="73"/>
+      <c r="BD16" s="71"/>
+      <c r="BE16" s="71"/>
+      <c r="BF16" s="71"/>
+      <c r="BG16" s="71"/>
+      <c r="BH16" s="71"/>
+      <c r="BI16" s="73"/>
+      <c r="BJ16" s="74"/>
+      <c r="BK16" s="62"/>
+      <c r="BL16" s="63"/>
+      <c r="BM16" s="64"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" s="65" t="n">
+        <f aca="false">Netzplan!J15</f>
+        <v>1</v>
+      </c>
+      <c r="H17" s="66" t="n">
+        <f aca="false">SUM(I17:BJ17)</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="71"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="71"/>
+      <c r="L17" s="71"/>
+      <c r="M17" s="71"/>
+      <c r="N17" s="71"/>
+      <c r="O17" s="71"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="71"/>
+      <c r="S17" s="71"/>
+      <c r="T17" s="71"/>
+      <c r="U17" s="71"/>
+      <c r="V17" s="71"/>
+      <c r="W17" s="71"/>
+      <c r="X17" s="71"/>
+      <c r="Y17" s="71"/>
+      <c r="Z17" s="71"/>
+      <c r="AA17" s="71"/>
+      <c r="AB17" s="71"/>
+      <c r="AC17" s="71"/>
+      <c r="AD17" s="71"/>
+      <c r="AE17" s="71"/>
+      <c r="AF17" s="71"/>
+      <c r="AG17" s="71"/>
+      <c r="AI17" s="71"/>
+      <c r="AJ17" s="71"/>
+      <c r="AL17" s="71"/>
+      <c r="AM17" s="71"/>
+      <c r="AO17" s="71"/>
+      <c r="AP17" s="71"/>
+      <c r="AQ17" s="71"/>
+      <c r="AR17" s="74"/>
+      <c r="AS17" s="72"/>
+      <c r="AT17" s="71"/>
+      <c r="AU17" s="71"/>
+      <c r="AV17" s="73"/>
+      <c r="AW17" s="71"/>
+      <c r="AX17" s="71"/>
+      <c r="AY17" s="71"/>
+      <c r="AZ17" s="71"/>
+      <c r="BA17" s="71"/>
+      <c r="BB17" s="71"/>
+      <c r="BC17" s="73"/>
+      <c r="BD17" s="71"/>
+      <c r="BE17" s="71"/>
+      <c r="BF17" s="71"/>
+      <c r="BG17" s="71"/>
+      <c r="BH17" s="71"/>
+      <c r="BI17" s="73"/>
+      <c r="BJ17" s="74"/>
+      <c r="BK17" s="62"/>
+      <c r="BL17" s="63"/>
+      <c r="BM17" s="64"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" s="65" t="n">
+        <f aca="false">Netzplan!J16</f>
+        <v>4</v>
+      </c>
+      <c r="H18" s="66" t="n">
+        <f aca="false">SUM(I18:BJ18)</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="71"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="71"/>
+      <c r="L18" s="71"/>
+      <c r="M18" s="71"/>
+      <c r="N18" s="71"/>
+      <c r="O18" s="71"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="71"/>
+      <c r="S18" s="71"/>
+      <c r="T18" s="71"/>
+      <c r="U18" s="71"/>
+      <c r="V18" s="71"/>
+      <c r="W18" s="71"/>
+      <c r="X18" s="71"/>
+      <c r="Y18" s="71"/>
+      <c r="Z18" s="71"/>
+      <c r="AA18" s="71"/>
+      <c r="AB18" s="71"/>
+      <c r="AC18" s="71"/>
+      <c r="AD18" s="71"/>
+      <c r="AE18" s="71"/>
+      <c r="AF18" s="71"/>
+      <c r="AG18" s="71"/>
+      <c r="AH18" s="71"/>
+      <c r="AI18" s="71"/>
+      <c r="AJ18" s="71"/>
+      <c r="AL18" s="71"/>
+      <c r="AM18" s="74"/>
+      <c r="AN18" s="74"/>
+      <c r="AO18" s="71"/>
+      <c r="AP18" s="71"/>
+      <c r="AQ18" s="71"/>
+      <c r="AR18" s="71"/>
+      <c r="AS18" s="71"/>
+      <c r="AT18" s="71"/>
+      <c r="AU18" s="72"/>
+      <c r="AV18" s="73"/>
+      <c r="AW18" s="71"/>
+      <c r="AX18" s="71"/>
+      <c r="AY18" s="72"/>
+      <c r="AZ18" s="72"/>
+      <c r="BA18" s="72"/>
+      <c r="BB18" s="71"/>
+      <c r="BC18" s="73"/>
+      <c r="BD18" s="71"/>
+      <c r="BE18" s="71"/>
+      <c r="BF18" s="71"/>
+      <c r="BG18" s="71"/>
+      <c r="BH18" s="71"/>
+      <c r="BI18" s="73"/>
+      <c r="BJ18" s="74"/>
+      <c r="BK18" s="62"/>
+      <c r="BL18" s="63"/>
+      <c r="BM18" s="64"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="45" t="s">
+        <v>60</v>
+      </c>
+      <c r="F19" s="46"/>
+      <c r="G19" s="65" t="n">
+        <f aca="false">Netzplan!J17</f>
+        <v>1</v>
+      </c>
+      <c r="H19" s="66" t="n">
+        <f aca="false">SUM(I19:BJ19)</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="77"/>
+      <c r="J19" s="77"/>
+      <c r="K19" s="77"/>
+      <c r="L19" s="77"/>
+      <c r="M19" s="77"/>
+      <c r="N19" s="77"/>
+      <c r="O19" s="77"/>
+      <c r="P19" s="77"/>
+      <c r="Q19" s="77"/>
+      <c r="R19" s="77"/>
+      <c r="S19" s="77"/>
+      <c r="T19" s="77"/>
+      <c r="U19" s="77"/>
+      <c r="V19" s="77"/>
+      <c r="W19" s="77"/>
+      <c r="X19" s="77"/>
+      <c r="Y19" s="77"/>
+      <c r="Z19" s="77"/>
+      <c r="AA19" s="77"/>
+      <c r="AB19" s="77"/>
+      <c r="AC19" s="77"/>
+      <c r="AD19" s="77"/>
+      <c r="AE19" s="77"/>
+      <c r="AF19" s="77"/>
+      <c r="AG19" s="77"/>
+      <c r="AH19" s="77"/>
+      <c r="AI19" s="77"/>
+      <c r="AJ19" s="77"/>
+      <c r="AK19" s="77"/>
+      <c r="AL19" s="77"/>
+      <c r="AM19" s="77"/>
+      <c r="AN19" s="77"/>
+      <c r="AO19" s="77"/>
+      <c r="AP19" s="77"/>
+      <c r="AQ19" s="77"/>
+      <c r="AR19" s="77"/>
+      <c r="AS19" s="77"/>
+      <c r="AT19" s="77"/>
+      <c r="AU19" s="77"/>
+      <c r="AV19" s="78"/>
+      <c r="AW19" s="77"/>
+      <c r="AX19" s="77"/>
+      <c r="AY19" s="79"/>
+      <c r="AZ19" s="79"/>
+      <c r="BA19" s="77"/>
+      <c r="BB19" s="77"/>
+      <c r="BC19" s="78"/>
+      <c r="BD19" s="77"/>
+      <c r="BE19" s="77"/>
+      <c r="BF19" s="77"/>
+      <c r="BG19" s="77"/>
+      <c r="BH19" s="77"/>
+      <c r="BI19" s="78"/>
+      <c r="BJ19" s="80"/>
+      <c r="BK19" s="62"/>
+      <c r="BL19" s="63"/>
+      <c r="BM19" s="64"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+  </mergeCells>
+  <conditionalFormatting sqref="I11:AC15 AE11:BF12 I19:BF19 AL16:BF16 AL17:AM17 AO17:BF17 I1:BF10 AD13:BF14 AE15:BF15 I16:AE16 AG16:AJ16 I17:AG17 I18:AJ18 AI17:AJ17 AL18:BF18">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>IF(OR(WEEKDAY(I$1)=7,WEEKDAY(I$1)=1),1,0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H19">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>IF(H2&lt;&gt;G2,TRUE())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I11:AC15 AE11:BF12 I19:BF19 AL16:BF16 AL17:AM17 AO17:BF17 I2:BF10 AD13:BF14 AE15:BF15 I16:AE16 AG16:AJ16 I17:AG17 I18:AJ18 AI17:AJ17 AL18:BF18">
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
--- a/Übungen/Onlineshop.xlsx
+++ b/Übungen/Onlineshop.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="81">
   <si>
     <t xml:space="preserve">Beispiel: Funktionsorientierter Projektstrukturplan</t>
   </si>
@@ -368,7 +368,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -415,6 +415,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFF8000"/>
         <bgColor rgb="FFFF6600"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF999999"/>
+        <bgColor rgb="FF808080"/>
       </patternFill>
     </fill>
     <fill>
@@ -537,7 +543,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="92">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -774,6 +780,14 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -782,7 +796,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="70" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="70" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="10" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="70" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -806,7 +824,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="9" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -814,6 +832,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -826,36 +852,60 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="9" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -976,7 +1026,7 @@
       <rgbColor rgb="FFFF8000"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666666"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF999999"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF00A933"/>
       <rgbColor rgb="FF003300"/>
@@ -1918,6 +1968,283 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>63720</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>153720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>190080</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>8280</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9192240" y="1640160"/>
+          <a:ext cx="126360" cy="179640"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:rect l="l" t="t" r="r" b="b"/>
+          <a:pathLst>
+            <a:path w="21600" h="21600">
+              <a:moveTo>
+                <a:pt x="10800" y="0"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="21600" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="0"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="729fcf"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>19080</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>9360</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>145440</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>26280</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11934720" y="2471040"/>
+          <a:ext cx="126360" cy="179640"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:rect l="l" t="t" r="r" b="b"/>
+          <a:pathLst>
+            <a:path w="21600" h="21600">
+              <a:moveTo>
+                <a:pt x="10800" y="0"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="21600" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="0"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="729fcf"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>57600</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>151560</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>183960</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>6120</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14000040" y="2938320"/>
+          <a:ext cx="126360" cy="179640"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:rect l="l" t="t" r="r" b="b"/>
+          <a:pathLst>
+            <a:path w="21600" h="21600">
+              <a:moveTo>
+                <a:pt x="10800" y="0"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="21600" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="0"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="729fcf"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>51</xdr:col>
+      <xdr:colOff>78120</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>5040</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>51</xdr:col>
+      <xdr:colOff>204480</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>22320</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17314560" y="3279600"/>
+          <a:ext cx="126360" cy="179640"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:rect l="l" t="t" r="r" b="b"/>
+          <a:pathLst>
+            <a:path w="21600" h="21600">
+              <a:moveTo>
+                <a:pt x="10800" y="0"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="21600" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="0"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="729fcf"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -3712,18 +4039,14 @@
       <c r="D22" s="55" t="s">
         <v>63</v>
       </c>
-      <c r="G22" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="H22" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="I22" s="21" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J22" s="3" t="n">
-        <f aca="false">G22/(H22*I22)</f>
-        <v>6.66666666666667</v>
+      <c r="G22" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I22" s="21" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3748,6 +4071,18 @@
       <c r="C24" s="31"/>
       <c r="D24" s="30" t="s">
         <v>68</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3888,6 +4223,7 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3899,11 +4235,17 @@
   <dimension ref="A1:BM22"/>
   <sheetFormatPr defaultColWidth="11.7578125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="1"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="5" min="5" style="0" width="16.2"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="6" min="6" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="1" max="5" min="5" style="0" width="16.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="1" max="6" min="6" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11.59"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="8" min="8" style="0" width="3.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="9" style="0" width="3.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="1" max="8" min="8" style="0" width="3.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="9" style="0" width="3.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="59" width="3.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="47" min="42" style="0" width="3.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="48" style="60" width="3.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="49" style="0" width="3.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="55" style="60" width="3.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="56" style="0" width="3.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="63" min="63" style="0" width="7.65"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="64" style="0" width="8.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="65" min="65" style="0" width="11.52"/>
@@ -3925,175 +4267,175 @@
       <c r="F1" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="G1" s="59" t="s">
+      <c r="G1" s="61" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="59"/>
-      <c r="I1" s="60" t="n">
-        <v>44515</v>
-      </c>
-      <c r="J1" s="60" t="n">
-        <v>44516</v>
-      </c>
-      <c r="K1" s="60" t="n">
-        <v>44517</v>
-      </c>
-      <c r="L1" s="60" t="n">
-        <v>44518</v>
-      </c>
-      <c r="M1" s="60" t="n">
-        <v>44519</v>
-      </c>
-      <c r="N1" s="60" t="n">
-        <v>44520</v>
-      </c>
-      <c r="O1" s="60" t="n">
-        <v>44521</v>
-      </c>
-      <c r="P1" s="60" t="n">
-        <v>44522</v>
-      </c>
-      <c r="Q1" s="60" t="n">
-        <v>44523</v>
-      </c>
-      <c r="R1" s="60" t="n">
-        <v>44524</v>
-      </c>
-      <c r="S1" s="60" t="n">
-        <v>44525</v>
-      </c>
-      <c r="T1" s="60" t="n">
-        <v>44526</v>
-      </c>
-      <c r="U1" s="60" t="n">
-        <v>44527</v>
-      </c>
-      <c r="V1" s="60" t="n">
-        <v>44528</v>
-      </c>
-      <c r="W1" s="60" t="n">
-        <v>44529</v>
-      </c>
-      <c r="X1" s="60" t="n">
-        <v>44530</v>
-      </c>
-      <c r="Y1" s="60" t="n">
-        <v>44531</v>
-      </c>
-      <c r="Z1" s="60" t="n">
-        <v>44532</v>
-      </c>
-      <c r="AA1" s="60" t="n">
-        <v>44533</v>
-      </c>
-      <c r="AB1" s="60" t="n">
-        <v>44534</v>
-      </c>
-      <c r="AC1" s="60" t="n">
-        <v>44535</v>
-      </c>
-      <c r="AD1" s="60" t="n">
-        <v>44536</v>
-      </c>
-      <c r="AE1" s="60" t="n">
-        <v>44537</v>
-      </c>
-      <c r="AF1" s="60" t="n">
-        <v>44538</v>
-      </c>
-      <c r="AG1" s="60" t="n">
-        <v>44539</v>
-      </c>
-      <c r="AH1" s="60" t="n">
-        <v>44540</v>
-      </c>
-      <c r="AI1" s="60" t="n">
-        <v>44541</v>
-      </c>
-      <c r="AJ1" s="60" t="n">
-        <v>44542</v>
-      </c>
-      <c r="AK1" s="60" t="n">
-        <v>44543</v>
-      </c>
-      <c r="AL1" s="60" t="n">
-        <v>44544</v>
-      </c>
-      <c r="AM1" s="60" t="n">
-        <v>44545</v>
-      </c>
-      <c r="AN1" s="60" t="n">
-        <v>44546</v>
-      </c>
-      <c r="AO1" s="60" t="n">
-        <v>44547</v>
-      </c>
-      <c r="AP1" s="60" t="n">
-        <v>44548</v>
-      </c>
-      <c r="AQ1" s="60" t="n">
-        <v>44549</v>
-      </c>
-      <c r="AR1" s="60" t="n">
-        <v>44550</v>
-      </c>
-      <c r="AS1" s="60" t="n">
-        <v>44551</v>
-      </c>
-      <c r="AT1" s="60" t="n">
-        <v>44552</v>
-      </c>
-      <c r="AU1" s="60" t="n">
-        <v>44553</v>
-      </c>
-      <c r="AV1" s="61" t="n">
-        <v>44554</v>
-      </c>
-      <c r="AW1" s="60" t="n">
-        <v>44555</v>
-      </c>
-      <c r="AX1" s="60" t="n">
-        <v>44556</v>
-      </c>
-      <c r="AY1" s="60" t="n">
-        <v>44557</v>
-      </c>
-      <c r="AZ1" s="60" t="n">
-        <v>44558</v>
-      </c>
-      <c r="BA1" s="60" t="n">
-        <v>44559</v>
-      </c>
-      <c r="BB1" s="60" t="n">
-        <v>44560</v>
-      </c>
-      <c r="BC1" s="61" t="n">
-        <v>44561</v>
-      </c>
-      <c r="BD1" s="60" t="n">
-        <v>44562</v>
-      </c>
-      <c r="BE1" s="60" t="n">
-        <v>44563</v>
-      </c>
-      <c r="BF1" s="60" t="n">
-        <v>44564</v>
-      </c>
-      <c r="BG1" s="60" t="n">
-        <v>44565</v>
-      </c>
-      <c r="BH1" s="60" t="n">
-        <v>44566</v>
-      </c>
-      <c r="BI1" s="61" t="n">
-        <v>44567</v>
-      </c>
-      <c r="BJ1" s="60" t="n">
-        <v>44568</v>
-      </c>
-      <c r="BK1" s="62"/>
-      <c r="BL1" s="63"/>
-      <c r="BM1" s="64"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="62" t="n">
+        <v>44634</v>
+      </c>
+      <c r="J1" s="62" t="n">
+        <v>44635</v>
+      </c>
+      <c r="K1" s="62" t="n">
+        <v>44636</v>
+      </c>
+      <c r="L1" s="62" t="n">
+        <v>44637</v>
+      </c>
+      <c r="M1" s="62" t="n">
+        <v>44638</v>
+      </c>
+      <c r="N1" s="62" t="n">
+        <v>44639</v>
+      </c>
+      <c r="O1" s="62" t="n">
+        <v>44640</v>
+      </c>
+      <c r="P1" s="62" t="n">
+        <v>44641</v>
+      </c>
+      <c r="Q1" s="62" t="n">
+        <v>44642</v>
+      </c>
+      <c r="R1" s="62" t="n">
+        <v>44643</v>
+      </c>
+      <c r="S1" s="62" t="n">
+        <v>44644</v>
+      </c>
+      <c r="T1" s="62" t="n">
+        <v>44645</v>
+      </c>
+      <c r="U1" s="62" t="n">
+        <v>44646</v>
+      </c>
+      <c r="V1" s="62" t="n">
+        <v>44647</v>
+      </c>
+      <c r="W1" s="62" t="n">
+        <v>44648</v>
+      </c>
+      <c r="X1" s="62" t="n">
+        <v>44649</v>
+      </c>
+      <c r="Y1" s="62" t="n">
+        <v>44650</v>
+      </c>
+      <c r="Z1" s="62" t="n">
+        <v>44651</v>
+      </c>
+      <c r="AA1" s="62" t="n">
+        <v>44652</v>
+      </c>
+      <c r="AB1" s="62" t="n">
+        <v>44653</v>
+      </c>
+      <c r="AC1" s="62" t="n">
+        <v>44654</v>
+      </c>
+      <c r="AD1" s="62" t="n">
+        <v>44655</v>
+      </c>
+      <c r="AE1" s="62" t="n">
+        <v>44656</v>
+      </c>
+      <c r="AF1" s="62" t="n">
+        <v>44657</v>
+      </c>
+      <c r="AG1" s="62" t="n">
+        <v>44658</v>
+      </c>
+      <c r="AH1" s="62" t="n">
+        <v>44659</v>
+      </c>
+      <c r="AI1" s="62" t="n">
+        <v>44660</v>
+      </c>
+      <c r="AJ1" s="62" t="n">
+        <v>44661</v>
+      </c>
+      <c r="AK1" s="62" t="n">
+        <v>44662</v>
+      </c>
+      <c r="AL1" s="62" t="n">
+        <v>44663</v>
+      </c>
+      <c r="AM1" s="62" t="n">
+        <v>44664</v>
+      </c>
+      <c r="AN1" s="62" t="n">
+        <v>44665</v>
+      </c>
+      <c r="AO1" s="63" t="n">
+        <v>44666</v>
+      </c>
+      <c r="AP1" s="62" t="n">
+        <v>44667</v>
+      </c>
+      <c r="AQ1" s="62" t="n">
+        <v>44668</v>
+      </c>
+      <c r="AR1" s="63" t="n">
+        <v>44669</v>
+      </c>
+      <c r="AS1" s="62" t="n">
+        <v>44670</v>
+      </c>
+      <c r="AT1" s="62" t="n">
+        <v>44671</v>
+      </c>
+      <c r="AU1" s="62" t="n">
+        <v>44672</v>
+      </c>
+      <c r="AV1" s="64" t="n">
+        <v>44673</v>
+      </c>
+      <c r="AW1" s="62" t="n">
+        <v>44674</v>
+      </c>
+      <c r="AX1" s="62" t="n">
+        <v>44675</v>
+      </c>
+      <c r="AY1" s="62" t="n">
+        <v>44676</v>
+      </c>
+      <c r="AZ1" s="62" t="n">
+        <v>44677</v>
+      </c>
+      <c r="BA1" s="62" t="n">
+        <v>44678</v>
+      </c>
+      <c r="BB1" s="62" t="n">
+        <v>44679</v>
+      </c>
+      <c r="BC1" s="64" t="n">
+        <v>44680</v>
+      </c>
+      <c r="BD1" s="62" t="n">
+        <v>44681</v>
+      </c>
+      <c r="BE1" s="62" t="n">
+        <v>44682</v>
+      </c>
+      <c r="BF1" s="62" t="n">
+        <v>44683</v>
+      </c>
+      <c r="BG1" s="62" t="n">
+        <v>44684</v>
+      </c>
+      <c r="BH1" s="62" t="n">
+        <v>44685</v>
+      </c>
+      <c r="BI1" s="62" t="n">
+        <v>44686</v>
+      </c>
+      <c r="BJ1" s="62" t="n">
+        <v>44687</v>
+      </c>
+      <c r="BK1" s="65"/>
+      <c r="BL1" s="66"/>
+      <c r="BM1" s="67"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
@@ -4108,71 +4450,75 @@
       <c r="F2" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="G2" s="65" t="n">
+      <c r="G2" s="68" t="n">
         <f aca="false">Netzplan!J2</f>
         <v>2</v>
       </c>
-      <c r="H2" s="66" t="n">
+      <c r="H2" s="69" t="n">
         <f aca="false">SUM(I2:BJ2)</f>
-        <v>0</v>
-      </c>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="68"/>
-      <c r="O2" s="68"/>
-      <c r="P2" s="68"/>
-      <c r="Q2" s="68"/>
-      <c r="R2" s="68"/>
-      <c r="S2" s="68"/>
-      <c r="T2" s="68"/>
-      <c r="U2" s="68"/>
-      <c r="V2" s="68"/>
-      <c r="W2" s="68"/>
-      <c r="X2" s="68"/>
-      <c r="Y2" s="68"/>
-      <c r="Z2" s="68"/>
-      <c r="AA2" s="68"/>
-      <c r="AB2" s="68"/>
-      <c r="AC2" s="68"/>
-      <c r="AD2" s="68"/>
-      <c r="AE2" s="68"/>
-      <c r="AF2" s="68"/>
-      <c r="AG2" s="68"/>
-      <c r="AH2" s="68"/>
-      <c r="AI2" s="68"/>
-      <c r="AJ2" s="68"/>
-      <c r="AK2" s="68"/>
-      <c r="AL2" s="68"/>
-      <c r="AM2" s="68"/>
-      <c r="AN2" s="68"/>
-      <c r="AO2" s="68"/>
-      <c r="AP2" s="68"/>
-      <c r="AQ2" s="68"/>
-      <c r="AR2" s="68"/>
-      <c r="AS2" s="68"/>
-      <c r="AT2" s="68"/>
-      <c r="AU2" s="68"/>
-      <c r="AV2" s="69"/>
-      <c r="AW2" s="68"/>
-      <c r="AX2" s="68"/>
-      <c r="AY2" s="68"/>
-      <c r="AZ2" s="68"/>
-      <c r="BA2" s="68"/>
-      <c r="BB2" s="68"/>
-      <c r="BC2" s="69"/>
-      <c r="BD2" s="68"/>
-      <c r="BE2" s="68"/>
-      <c r="BF2" s="68"/>
-      <c r="BG2" s="68"/>
-      <c r="BH2" s="68"/>
-      <c r="BI2" s="69"/>
-      <c r="BJ2" s="70"/>
-      <c r="BK2" s="62"/>
-      <c r="BL2" s="63"/>
-      <c r="BM2" s="64"/>
+        <v>2</v>
+      </c>
+      <c r="I2" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
+      <c r="N2" s="71"/>
+      <c r="O2" s="71"/>
+      <c r="P2" s="71"/>
+      <c r="Q2" s="71"/>
+      <c r="R2" s="71"/>
+      <c r="S2" s="71"/>
+      <c r="T2" s="71"/>
+      <c r="U2" s="71"/>
+      <c r="V2" s="71"/>
+      <c r="W2" s="71"/>
+      <c r="X2" s="71"/>
+      <c r="Y2" s="71"/>
+      <c r="Z2" s="71"/>
+      <c r="AA2" s="71"/>
+      <c r="AB2" s="71"/>
+      <c r="AC2" s="71"/>
+      <c r="AD2" s="71"/>
+      <c r="AE2" s="71"/>
+      <c r="AF2" s="71"/>
+      <c r="AG2" s="71"/>
+      <c r="AH2" s="71"/>
+      <c r="AI2" s="71"/>
+      <c r="AJ2" s="71"/>
+      <c r="AK2" s="71"/>
+      <c r="AL2" s="71"/>
+      <c r="AM2" s="71"/>
+      <c r="AN2" s="71"/>
+      <c r="AO2" s="72"/>
+      <c r="AP2" s="71"/>
+      <c r="AQ2" s="71"/>
+      <c r="AR2" s="72"/>
+      <c r="AS2" s="71"/>
+      <c r="AT2" s="71"/>
+      <c r="AU2" s="71"/>
+      <c r="AV2" s="73"/>
+      <c r="AW2" s="71"/>
+      <c r="AX2" s="71"/>
+      <c r="AY2" s="71"/>
+      <c r="AZ2" s="71"/>
+      <c r="BA2" s="71"/>
+      <c r="BB2" s="71"/>
+      <c r="BC2" s="73"/>
+      <c r="BD2" s="71"/>
+      <c r="BE2" s="71"/>
+      <c r="BF2" s="71"/>
+      <c r="BG2" s="71"/>
+      <c r="BH2" s="71"/>
+      <c r="BI2" s="74"/>
+      <c r="BJ2" s="75"/>
+      <c r="BK2" s="65"/>
+      <c r="BL2" s="66"/>
+      <c r="BM2" s="67"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
@@ -4189,71 +4535,73 @@
       <c r="F3" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="65" t="n">
+      <c r="G3" s="68" t="n">
         <f aca="false">Netzplan!J3</f>
         <v>1</v>
       </c>
-      <c r="H3" s="66" t="n">
+      <c r="H3" s="69" t="n">
         <f aca="false">SUM(I3:BJ3)</f>
-        <v>0</v>
-      </c>
-      <c r="I3" s="71"/>
-      <c r="J3" s="71"/>
-      <c r="K3" s="71"/>
-      <c r="L3" s="71"/>
-      <c r="M3" s="71"/>
-      <c r="N3" s="71"/>
-      <c r="O3" s="71"/>
-      <c r="P3" s="72"/>
-      <c r="Q3" s="71"/>
-      <c r="R3" s="71"/>
-      <c r="S3" s="71"/>
-      <c r="T3" s="71"/>
-      <c r="U3" s="71"/>
-      <c r="V3" s="71"/>
-      <c r="W3" s="71"/>
-      <c r="X3" s="71"/>
-      <c r="Y3" s="71"/>
-      <c r="Z3" s="71"/>
-      <c r="AA3" s="71"/>
-      <c r="AB3" s="71"/>
-      <c r="AC3" s="71"/>
-      <c r="AD3" s="71"/>
-      <c r="AE3" s="71"/>
-      <c r="AF3" s="71"/>
-      <c r="AG3" s="71"/>
-      <c r="AH3" s="71"/>
-      <c r="AI3" s="71"/>
-      <c r="AJ3" s="71"/>
-      <c r="AK3" s="71"/>
-      <c r="AL3" s="71"/>
-      <c r="AM3" s="71"/>
-      <c r="AN3" s="71"/>
-      <c r="AO3" s="71"/>
-      <c r="AP3" s="71"/>
-      <c r="AQ3" s="71"/>
-      <c r="AR3" s="71"/>
-      <c r="AS3" s="71"/>
-      <c r="AT3" s="71"/>
-      <c r="AU3" s="71"/>
-      <c r="AV3" s="73"/>
-      <c r="AW3" s="71"/>
-      <c r="AX3" s="71"/>
-      <c r="AY3" s="71"/>
-      <c r="AZ3" s="71"/>
-      <c r="BA3" s="71"/>
-      <c r="BB3" s="71"/>
-      <c r="BC3" s="73"/>
-      <c r="BD3" s="71"/>
-      <c r="BE3" s="71"/>
-      <c r="BF3" s="71"/>
-      <c r="BG3" s="71"/>
-      <c r="BH3" s="71"/>
-      <c r="BI3" s="73"/>
-      <c r="BJ3" s="74"/>
-      <c r="BK3" s="62"/>
-      <c r="BL3" s="63"/>
-      <c r="BM3" s="64"/>
+        <v>1</v>
+      </c>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
+      <c r="K3" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="76"/>
+      <c r="M3" s="76"/>
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="W3" s="76"/>
+      <c r="X3" s="76"/>
+      <c r="Y3" s="76"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="76"/>
+      <c r="AB3" s="76"/>
+      <c r="AC3" s="76"/>
+      <c r="AD3" s="76"/>
+      <c r="AE3" s="76"/>
+      <c r="AF3" s="76"/>
+      <c r="AG3" s="76"/>
+      <c r="AH3" s="76"/>
+      <c r="AI3" s="76"/>
+      <c r="AJ3" s="76"/>
+      <c r="AK3" s="76"/>
+      <c r="AL3" s="76"/>
+      <c r="AM3" s="76"/>
+      <c r="AN3" s="76"/>
+      <c r="AO3" s="78"/>
+      <c r="AP3" s="76"/>
+      <c r="AQ3" s="76"/>
+      <c r="AR3" s="78"/>
+      <c r="AS3" s="76"/>
+      <c r="AT3" s="76"/>
+      <c r="AU3" s="76"/>
+      <c r="AV3" s="79"/>
+      <c r="AW3" s="76"/>
+      <c r="AX3" s="76"/>
+      <c r="AY3" s="76"/>
+      <c r="AZ3" s="76"/>
+      <c r="BA3" s="76"/>
+      <c r="BB3" s="76"/>
+      <c r="BC3" s="79"/>
+      <c r="BD3" s="76"/>
+      <c r="BE3" s="76"/>
+      <c r="BF3" s="76"/>
+      <c r="BG3" s="76"/>
+      <c r="BH3" s="76"/>
+      <c r="BI3" s="80"/>
+      <c r="BJ3" s="81"/>
+      <c r="BK3" s="65"/>
+      <c r="BL3" s="66"/>
+      <c r="BM3" s="67"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
@@ -4270,71 +4618,83 @@
       <c r="F4" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="65" t="n">
+      <c r="G4" s="68" t="n">
         <f aca="false">Netzplan!J4</f>
         <v>6</v>
       </c>
-      <c r="H4" s="66" t="n">
+      <c r="H4" s="69" t="n">
         <f aca="false">SUM(I4:BJ4)</f>
-        <v>0</v>
-      </c>
-      <c r="I4" s="71"/>
-      <c r="J4" s="71"/>
-      <c r="K4" s="71"/>
-      <c r="L4" s="71"/>
-      <c r="M4" s="71"/>
-      <c r="N4" s="71"/>
-      <c r="O4" s="71"/>
-      <c r="P4" s="71"/>
-      <c r="Q4" s="72"/>
-      <c r="R4" s="72"/>
-      <c r="S4" s="72"/>
-      <c r="T4" s="72"/>
-      <c r="U4" s="71"/>
-      <c r="V4" s="71"/>
-      <c r="W4" s="71"/>
-      <c r="X4" s="71"/>
-      <c r="Y4" s="71"/>
-      <c r="Z4" s="71"/>
-      <c r="AA4" s="71"/>
-      <c r="AB4" s="71"/>
-      <c r="AC4" s="71"/>
-      <c r="AD4" s="71"/>
-      <c r="AE4" s="71"/>
-      <c r="AF4" s="71"/>
-      <c r="AG4" s="71"/>
-      <c r="AH4" s="71"/>
-      <c r="AI4" s="71"/>
-      <c r="AJ4" s="71"/>
-      <c r="AK4" s="71"/>
-      <c r="AL4" s="71"/>
-      <c r="AM4" s="71"/>
-      <c r="AN4" s="71"/>
-      <c r="AO4" s="71"/>
-      <c r="AP4" s="71"/>
-      <c r="AQ4" s="71"/>
-      <c r="AR4" s="71"/>
-      <c r="AS4" s="71"/>
-      <c r="AT4" s="71"/>
-      <c r="AU4" s="71"/>
-      <c r="AV4" s="73"/>
-      <c r="AW4" s="71"/>
-      <c r="AX4" s="71"/>
-      <c r="AY4" s="71"/>
-      <c r="AZ4" s="71"/>
-      <c r="BA4" s="71"/>
-      <c r="BB4" s="71"/>
-      <c r="BC4" s="73"/>
-      <c r="BD4" s="71"/>
-      <c r="BE4" s="71"/>
-      <c r="BF4" s="71"/>
-      <c r="BG4" s="71"/>
-      <c r="BH4" s="71"/>
-      <c r="BI4" s="73"/>
-      <c r="BJ4" s="74"/>
-      <c r="BK4" s="62"/>
-      <c r="BL4" s="63"/>
-      <c r="BM4" s="64"/>
+        <v>6</v>
+      </c>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
+      <c r="K4" s="76"/>
+      <c r="L4" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" s="77"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="W4" s="76"/>
+      <c r="X4" s="76"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
+      <c r="AB4" s="76"/>
+      <c r="AC4" s="76"/>
+      <c r="AD4" s="76"/>
+      <c r="AE4" s="76"/>
+      <c r="AF4" s="76"/>
+      <c r="AG4" s="76"/>
+      <c r="AH4" s="76"/>
+      <c r="AI4" s="76"/>
+      <c r="AJ4" s="76"/>
+      <c r="AK4" s="76"/>
+      <c r="AL4" s="76"/>
+      <c r="AM4" s="76"/>
+      <c r="AN4" s="76"/>
+      <c r="AO4" s="78"/>
+      <c r="AP4" s="76"/>
+      <c r="AQ4" s="76"/>
+      <c r="AR4" s="78"/>
+      <c r="AS4" s="76"/>
+      <c r="AT4" s="76"/>
+      <c r="AU4" s="76"/>
+      <c r="AV4" s="79"/>
+      <c r="AW4" s="76"/>
+      <c r="AX4" s="76"/>
+      <c r="AY4" s="76"/>
+      <c r="AZ4" s="76"/>
+      <c r="BA4" s="76"/>
+      <c r="BB4" s="76"/>
+      <c r="BC4" s="79"/>
+      <c r="BD4" s="76"/>
+      <c r="BE4" s="76"/>
+      <c r="BF4" s="76"/>
+      <c r="BG4" s="76"/>
+      <c r="BH4" s="76"/>
+      <c r="BI4" s="80"/>
+      <c r="BJ4" s="81"/>
+      <c r="BK4" s="65"/>
+      <c r="BL4" s="66"/>
+      <c r="BM4" s="67"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
@@ -4351,71 +4711,75 @@
       <c r="F5" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="65" t="n">
+      <c r="G5" s="68" t="n">
         <f aca="false">Netzplan!J5</f>
         <v>2</v>
       </c>
-      <c r="H5" s="66" t="n">
+      <c r="H5" s="69" t="n">
         <f aca="false">SUM(I5:BJ5)</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="71"/>
-      <c r="J5" s="71"/>
-      <c r="K5" s="71"/>
-      <c r="L5" s="72"/>
-      <c r="M5" s="72"/>
-      <c r="N5" s="71"/>
-      <c r="O5" s="71"/>
-      <c r="P5" s="71"/>
-      <c r="Q5" s="72"/>
-      <c r="R5" s="72"/>
-      <c r="S5" s="75"/>
-      <c r="T5" s="71"/>
-      <c r="U5" s="71"/>
-      <c r="V5" s="71"/>
-      <c r="W5" s="71"/>
-      <c r="X5" s="71"/>
-      <c r="Y5" s="71"/>
-      <c r="Z5" s="71"/>
-      <c r="AA5" s="71"/>
-      <c r="AB5" s="71"/>
-      <c r="AC5" s="71"/>
-      <c r="AD5" s="71"/>
-      <c r="AE5" s="71"/>
-      <c r="AF5" s="71"/>
-      <c r="AG5" s="71"/>
-      <c r="AH5" s="71"/>
-      <c r="AI5" s="71"/>
-      <c r="AJ5" s="71"/>
-      <c r="AK5" s="71"/>
-      <c r="AL5" s="71"/>
-      <c r="AM5" s="71"/>
-      <c r="AN5" s="71"/>
-      <c r="AO5" s="71"/>
-      <c r="AP5" s="71"/>
-      <c r="AQ5" s="71"/>
-      <c r="AR5" s="71"/>
-      <c r="AS5" s="71"/>
-      <c r="AT5" s="71"/>
-      <c r="AU5" s="71"/>
-      <c r="AV5" s="73"/>
-      <c r="AW5" s="71"/>
-      <c r="AX5" s="71"/>
-      <c r="AY5" s="71"/>
-      <c r="AZ5" s="71"/>
-      <c r="BA5" s="71"/>
-      <c r="BB5" s="71"/>
-      <c r="BC5" s="73"/>
-      <c r="BD5" s="71"/>
-      <c r="BE5" s="71"/>
-      <c r="BF5" s="71"/>
-      <c r="BG5" s="71"/>
-      <c r="BH5" s="71"/>
-      <c r="BI5" s="73"/>
-      <c r="BJ5" s="74"/>
-      <c r="BK5" s="62"/>
-      <c r="BL5" s="63"/>
-      <c r="BM5" s="64"/>
+        <v>2</v>
+      </c>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
+      <c r="K5" s="76"/>
+      <c r="L5" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="82"/>
+      <c r="T5" s="76"/>
+      <c r="U5" s="76"/>
+      <c r="V5" s="76"/>
+      <c r="W5" s="76"/>
+      <c r="X5" s="76"/>
+      <c r="Y5" s="76"/>
+      <c r="Z5" s="76"/>
+      <c r="AA5" s="76"/>
+      <c r="AB5" s="76"/>
+      <c r="AC5" s="76"/>
+      <c r="AD5" s="76"/>
+      <c r="AE5" s="76"/>
+      <c r="AF5" s="76"/>
+      <c r="AG5" s="76"/>
+      <c r="AH5" s="76"/>
+      <c r="AI5" s="76"/>
+      <c r="AJ5" s="76"/>
+      <c r="AK5" s="76"/>
+      <c r="AL5" s="76"/>
+      <c r="AM5" s="76"/>
+      <c r="AN5" s="76"/>
+      <c r="AO5" s="78"/>
+      <c r="AP5" s="76"/>
+      <c r="AQ5" s="76"/>
+      <c r="AR5" s="78"/>
+      <c r="AS5" s="76"/>
+      <c r="AT5" s="76"/>
+      <c r="AU5" s="76"/>
+      <c r="AV5" s="79"/>
+      <c r="AW5" s="76"/>
+      <c r="AX5" s="76"/>
+      <c r="AY5" s="76"/>
+      <c r="AZ5" s="76"/>
+      <c r="BA5" s="76"/>
+      <c r="BB5" s="76"/>
+      <c r="BC5" s="79"/>
+      <c r="BD5" s="76"/>
+      <c r="BE5" s="76"/>
+      <c r="BF5" s="76"/>
+      <c r="BG5" s="76"/>
+      <c r="BH5" s="76"/>
+      <c r="BI5" s="80"/>
+      <c r="BJ5" s="81"/>
+      <c r="BK5" s="65"/>
+      <c r="BL5" s="66"/>
+      <c r="BM5" s="67"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
@@ -4432,71 +4796,79 @@
       <c r="F6" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="65" t="n">
+      <c r="G6" s="68" t="n">
         <f aca="false">Netzplan!J6</f>
         <v>4</v>
       </c>
-      <c r="H6" s="66" t="n">
+      <c r="H6" s="69" t="n">
         <f aca="false">SUM(I6:BJ6)</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="71"/>
-      <c r="J6" s="71"/>
-      <c r="K6" s="71"/>
-      <c r="L6" s="71"/>
-      <c r="M6" s="71"/>
-      <c r="N6" s="71"/>
-      <c r="O6" s="71"/>
-      <c r="P6" s="72"/>
-      <c r="Q6" s="72"/>
-      <c r="R6" s="72"/>
-      <c r="S6" s="72"/>
-      <c r="T6" s="72"/>
-      <c r="U6" s="71"/>
-      <c r="V6" s="71"/>
-      <c r="W6" s="72"/>
-      <c r="X6" s="72"/>
-      <c r="Y6" s="72"/>
-      <c r="Z6" s="72"/>
-      <c r="AA6" s="75"/>
-      <c r="AB6" s="71"/>
-      <c r="AC6" s="71"/>
-      <c r="AD6" s="71"/>
-      <c r="AE6" s="71"/>
-      <c r="AF6" s="71"/>
-      <c r="AG6" s="71"/>
-      <c r="AH6" s="71"/>
-      <c r="AI6" s="71"/>
-      <c r="AJ6" s="71"/>
-      <c r="AK6" s="71"/>
-      <c r="AL6" s="71"/>
-      <c r="AM6" s="71"/>
-      <c r="AN6" s="71"/>
-      <c r="AO6" s="71"/>
-      <c r="AP6" s="71"/>
-      <c r="AQ6" s="71"/>
-      <c r="AR6" s="71"/>
-      <c r="AS6" s="71"/>
-      <c r="AT6" s="71"/>
-      <c r="AU6" s="71"/>
-      <c r="AV6" s="73"/>
-      <c r="AW6" s="71"/>
-      <c r="AX6" s="71"/>
-      <c r="AY6" s="71"/>
-      <c r="AZ6" s="71"/>
-      <c r="BA6" s="71"/>
-      <c r="BB6" s="71"/>
-      <c r="BC6" s="73"/>
-      <c r="BD6" s="71"/>
-      <c r="BE6" s="71"/>
-      <c r="BF6" s="71"/>
-      <c r="BG6" s="71"/>
-      <c r="BH6" s="71"/>
-      <c r="BI6" s="73"/>
-      <c r="BJ6" s="74"/>
-      <c r="BK6" s="62"/>
-      <c r="BL6" s="63"/>
-      <c r="BM6" s="64"/>
+        <v>4</v>
+      </c>
+      <c r="I6" s="76"/>
+      <c r="J6" s="76"/>
+      <c r="K6" s="76"/>
+      <c r="L6" s="76"/>
+      <c r="M6" s="76"/>
+      <c r="N6" s="76"/>
+      <c r="O6" s="76"/>
+      <c r="P6" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" s="77"/>
+      <c r="U6" s="76"/>
+      <c r="V6" s="76"/>
+      <c r="W6" s="77"/>
+      <c r="X6" s="77"/>
+      <c r="Y6" s="77"/>
+      <c r="Z6" s="77"/>
+      <c r="AA6" s="82"/>
+      <c r="AB6" s="76"/>
+      <c r="AC6" s="76"/>
+      <c r="AD6" s="76"/>
+      <c r="AE6" s="76"/>
+      <c r="AF6" s="76"/>
+      <c r="AG6" s="76"/>
+      <c r="AH6" s="76"/>
+      <c r="AI6" s="76"/>
+      <c r="AJ6" s="76"/>
+      <c r="AK6" s="76"/>
+      <c r="AL6" s="76"/>
+      <c r="AM6" s="76"/>
+      <c r="AN6" s="76"/>
+      <c r="AO6" s="78"/>
+      <c r="AP6" s="76"/>
+      <c r="AQ6" s="76"/>
+      <c r="AR6" s="78"/>
+      <c r="AS6" s="76"/>
+      <c r="AT6" s="76"/>
+      <c r="AU6" s="76"/>
+      <c r="AV6" s="79"/>
+      <c r="AW6" s="76"/>
+      <c r="AX6" s="76"/>
+      <c r="AY6" s="76"/>
+      <c r="AZ6" s="76"/>
+      <c r="BA6" s="76"/>
+      <c r="BB6" s="76"/>
+      <c r="BC6" s="79"/>
+      <c r="BD6" s="76"/>
+      <c r="BE6" s="76"/>
+      <c r="BF6" s="76"/>
+      <c r="BG6" s="76"/>
+      <c r="BH6" s="76"/>
+      <c r="BI6" s="80"/>
+      <c r="BJ6" s="81"/>
+      <c r="BK6" s="65"/>
+      <c r="BL6" s="66"/>
+      <c r="BM6" s="67"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
@@ -4513,71 +4885,73 @@
       <c r="F7" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="65" t="n">
+      <c r="G7" s="68" t="n">
         <f aca="false">Netzplan!J7</f>
         <v>1</v>
       </c>
-      <c r="H7" s="66" t="n">
+      <c r="H7" s="69" t="n">
         <f aca="false">SUM(I7:BJ7)</f>
-        <v>0</v>
-      </c>
-      <c r="I7" s="71"/>
-      <c r="J7" s="71"/>
-      <c r="K7" s="71"/>
-      <c r="L7" s="71"/>
-      <c r="M7" s="71"/>
-      <c r="N7" s="71"/>
-      <c r="O7" s="71"/>
-      <c r="P7" s="72"/>
-      <c r="Q7" s="71"/>
-      <c r="R7" s="71"/>
-      <c r="S7" s="71"/>
-      <c r="T7" s="71"/>
-      <c r="U7" s="71"/>
-      <c r="V7" s="71"/>
-      <c r="W7" s="71"/>
-      <c r="X7" s="71"/>
-      <c r="Y7" s="71"/>
-      <c r="Z7" s="71"/>
-      <c r="AA7" s="71"/>
-      <c r="AB7" s="71"/>
-      <c r="AC7" s="71"/>
-      <c r="AD7" s="71"/>
-      <c r="AE7" s="71"/>
-      <c r="AF7" s="71"/>
-      <c r="AG7" s="71"/>
-      <c r="AH7" s="71"/>
-      <c r="AI7" s="71"/>
-      <c r="AJ7" s="71"/>
-      <c r="AK7" s="71"/>
-      <c r="AL7" s="71"/>
-      <c r="AM7" s="71"/>
-      <c r="AN7" s="71"/>
-      <c r="AO7" s="71"/>
-      <c r="AP7" s="71"/>
-      <c r="AQ7" s="71"/>
-      <c r="AR7" s="71"/>
-      <c r="AS7" s="71"/>
-      <c r="AT7" s="71"/>
-      <c r="AU7" s="71"/>
-      <c r="AV7" s="73"/>
-      <c r="AW7" s="71"/>
-      <c r="AX7" s="71"/>
-      <c r="AY7" s="71"/>
-      <c r="AZ7" s="71"/>
-      <c r="BA7" s="71"/>
-      <c r="BB7" s="71"/>
-      <c r="BC7" s="73"/>
-      <c r="BD7" s="71"/>
-      <c r="BE7" s="71"/>
-      <c r="BF7" s="71"/>
-      <c r="BG7" s="71"/>
-      <c r="BH7" s="71"/>
-      <c r="BI7" s="73"/>
-      <c r="BJ7" s="74"/>
-      <c r="BK7" s="62"/>
-      <c r="BL7" s="63"/>
-      <c r="BM7" s="64"/>
+        <v>1</v>
+      </c>
+      <c r="I7" s="76"/>
+      <c r="J7" s="76"/>
+      <c r="K7" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="76"/>
+      <c r="M7" s="76"/>
+      <c r="N7" s="76"/>
+      <c r="O7" s="76"/>
+      <c r="P7" s="77"/>
+      <c r="Q7" s="76"/>
+      <c r="R7" s="76"/>
+      <c r="S7" s="76"/>
+      <c r="T7" s="76"/>
+      <c r="U7" s="76"/>
+      <c r="V7" s="76"/>
+      <c r="W7" s="76"/>
+      <c r="X7" s="76"/>
+      <c r="Y7" s="76"/>
+      <c r="Z7" s="76"/>
+      <c r="AA7" s="76"/>
+      <c r="AB7" s="76"/>
+      <c r="AC7" s="76"/>
+      <c r="AD7" s="76"/>
+      <c r="AE7" s="76"/>
+      <c r="AF7" s="76"/>
+      <c r="AG7" s="76"/>
+      <c r="AH7" s="76"/>
+      <c r="AI7" s="76"/>
+      <c r="AJ7" s="76"/>
+      <c r="AK7" s="76"/>
+      <c r="AL7" s="76"/>
+      <c r="AM7" s="76"/>
+      <c r="AN7" s="76"/>
+      <c r="AO7" s="78"/>
+      <c r="AP7" s="76"/>
+      <c r="AQ7" s="76"/>
+      <c r="AR7" s="78"/>
+      <c r="AS7" s="76"/>
+      <c r="AT7" s="76"/>
+      <c r="AU7" s="76"/>
+      <c r="AV7" s="79"/>
+      <c r="AW7" s="76"/>
+      <c r="AX7" s="76"/>
+      <c r="AY7" s="76"/>
+      <c r="AZ7" s="76"/>
+      <c r="BA7" s="76"/>
+      <c r="BB7" s="76"/>
+      <c r="BC7" s="79"/>
+      <c r="BD7" s="76"/>
+      <c r="BE7" s="76"/>
+      <c r="BF7" s="76"/>
+      <c r="BG7" s="76"/>
+      <c r="BH7" s="76"/>
+      <c r="BI7" s="80"/>
+      <c r="BJ7" s="81"/>
+      <c r="BK7" s="65"/>
+      <c r="BL7" s="66"/>
+      <c r="BM7" s="67"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
@@ -4594,71 +4968,83 @@
       <c r="F8" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="65" t="n">
+      <c r="G8" s="68" t="n">
         <f aca="false">Netzplan!J8</f>
         <v>6</v>
       </c>
-      <c r="H8" s="66" t="n">
+      <c r="H8" s="69" t="n">
         <f aca="false">SUM(I8:BJ8)</f>
-        <v>0</v>
-      </c>
-      <c r="I8" s="71"/>
-      <c r="J8" s="71"/>
-      <c r="K8" s="71"/>
-      <c r="L8" s="72"/>
-      <c r="M8" s="72"/>
-      <c r="N8" s="71"/>
-      <c r="O8" s="71"/>
-      <c r="P8" s="72"/>
-      <c r="Q8" s="72"/>
-      <c r="R8" s="72"/>
-      <c r="S8" s="72"/>
-      <c r="T8" s="71"/>
-      <c r="U8" s="71"/>
-      <c r="V8" s="71"/>
-      <c r="W8" s="71"/>
-      <c r="X8" s="71"/>
-      <c r="Y8" s="71"/>
-      <c r="Z8" s="71"/>
-      <c r="AA8" s="71"/>
-      <c r="AB8" s="71"/>
-      <c r="AC8" s="71"/>
-      <c r="AD8" s="71"/>
-      <c r="AE8" s="71"/>
-      <c r="AF8" s="71"/>
-      <c r="AG8" s="71"/>
-      <c r="AH8" s="71"/>
-      <c r="AI8" s="71"/>
-      <c r="AJ8" s="71"/>
-      <c r="AK8" s="71"/>
-      <c r="AL8" s="71"/>
-      <c r="AM8" s="71"/>
-      <c r="AN8" s="71"/>
-      <c r="AO8" s="71"/>
-      <c r="AP8" s="71"/>
-      <c r="AQ8" s="71"/>
-      <c r="AR8" s="71"/>
-      <c r="AS8" s="71"/>
-      <c r="AT8" s="71"/>
-      <c r="AU8" s="71"/>
-      <c r="AV8" s="73"/>
-      <c r="AW8" s="71"/>
-      <c r="AX8" s="71"/>
-      <c r="AY8" s="71"/>
-      <c r="AZ8" s="71"/>
-      <c r="BA8" s="71"/>
-      <c r="BB8" s="71"/>
-      <c r="BC8" s="73"/>
-      <c r="BD8" s="71"/>
-      <c r="BE8" s="71"/>
-      <c r="BF8" s="71"/>
-      <c r="BG8" s="71"/>
-      <c r="BH8" s="71"/>
-      <c r="BI8" s="73"/>
-      <c r="BJ8" s="74"/>
-      <c r="BK8" s="62"/>
-      <c r="BL8" s="63"/>
-      <c r="BM8" s="64"/>
+        <v>6</v>
+      </c>
+      <c r="I8" s="76"/>
+      <c r="J8" s="76"/>
+      <c r="K8" s="76"/>
+      <c r="L8" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="76"/>
+      <c r="O8" s="76"/>
+      <c r="P8" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" s="76"/>
+      <c r="U8" s="76"/>
+      <c r="V8" s="76"/>
+      <c r="W8" s="76"/>
+      <c r="X8" s="76"/>
+      <c r="Y8" s="76"/>
+      <c r="Z8" s="76"/>
+      <c r="AA8" s="76"/>
+      <c r="AB8" s="76"/>
+      <c r="AC8" s="76"/>
+      <c r="AD8" s="76"/>
+      <c r="AE8" s="76"/>
+      <c r="AF8" s="76"/>
+      <c r="AG8" s="76"/>
+      <c r="AH8" s="76"/>
+      <c r="AI8" s="76"/>
+      <c r="AJ8" s="76"/>
+      <c r="AK8" s="76"/>
+      <c r="AL8" s="76"/>
+      <c r="AM8" s="76"/>
+      <c r="AN8" s="76"/>
+      <c r="AO8" s="78"/>
+      <c r="AP8" s="76"/>
+      <c r="AQ8" s="76"/>
+      <c r="AR8" s="78"/>
+      <c r="AS8" s="76"/>
+      <c r="AT8" s="76"/>
+      <c r="AU8" s="76"/>
+      <c r="AV8" s="79"/>
+      <c r="AW8" s="76"/>
+      <c r="AX8" s="76"/>
+      <c r="AY8" s="76"/>
+      <c r="AZ8" s="76"/>
+      <c r="BA8" s="76"/>
+      <c r="BB8" s="76"/>
+      <c r="BC8" s="79"/>
+      <c r="BD8" s="76"/>
+      <c r="BE8" s="76"/>
+      <c r="BF8" s="76"/>
+      <c r="BG8" s="76"/>
+      <c r="BH8" s="76"/>
+      <c r="BI8" s="80"/>
+      <c r="BJ8" s="81"/>
+      <c r="BK8" s="65"/>
+      <c r="BL8" s="66"/>
+      <c r="BM8" s="67"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14"/>
@@ -4669,65 +5055,65 @@
       <c r="D9" s="42"/>
       <c r="E9" s="41"/>
       <c r="F9" s="41"/>
-      <c r="G9" s="65"/>
-      <c r="H9" s="66"/>
-      <c r="I9" s="71"/>
-      <c r="J9" s="71"/>
-      <c r="K9" s="71"/>
-      <c r="L9" s="72"/>
-      <c r="M9" s="72"/>
-      <c r="N9" s="71"/>
-      <c r="O9" s="71"/>
-      <c r="P9" s="72"/>
-      <c r="Q9" s="72"/>
-      <c r="R9" s="72"/>
-      <c r="S9" s="72"/>
-      <c r="T9" s="71"/>
-      <c r="U9" s="71"/>
-      <c r="V9" s="71"/>
-      <c r="W9" s="71"/>
-      <c r="X9" s="71"/>
-      <c r="Y9" s="71"/>
-      <c r="Z9" s="71"/>
-      <c r="AA9" s="71"/>
-      <c r="AB9" s="71"/>
-      <c r="AC9" s="71"/>
-      <c r="AD9" s="71"/>
-      <c r="AE9" s="71"/>
-      <c r="AF9" s="71"/>
-      <c r="AG9" s="71"/>
-      <c r="AH9" s="71"/>
-      <c r="AI9" s="71"/>
-      <c r="AJ9" s="71"/>
-      <c r="AK9" s="71"/>
-      <c r="AL9" s="71"/>
-      <c r="AM9" s="71"/>
-      <c r="AN9" s="71"/>
-      <c r="AO9" s="71"/>
-      <c r="AP9" s="71"/>
-      <c r="AQ9" s="71"/>
-      <c r="AR9" s="71"/>
-      <c r="AS9" s="71"/>
-      <c r="AT9" s="71"/>
-      <c r="AU9" s="71"/>
-      <c r="AV9" s="73"/>
-      <c r="AW9" s="71"/>
-      <c r="AX9" s="71"/>
-      <c r="AY9" s="71"/>
-      <c r="AZ9" s="71"/>
-      <c r="BA9" s="71"/>
-      <c r="BB9" s="71"/>
-      <c r="BC9" s="73"/>
-      <c r="BD9" s="71"/>
-      <c r="BE9" s="71"/>
-      <c r="BF9" s="71"/>
-      <c r="BG9" s="71"/>
-      <c r="BH9" s="71"/>
-      <c r="BI9" s="73"/>
-      <c r="BJ9" s="74"/>
-      <c r="BK9" s="62"/>
-      <c r="BL9" s="63"/>
-      <c r="BM9" s="64"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="69"/>
+      <c r="I9" s="76"/>
+      <c r="J9" s="76"/>
+      <c r="K9" s="76"/>
+      <c r="L9" s="77"/>
+      <c r="M9" s="77"/>
+      <c r="N9" s="76"/>
+      <c r="O9" s="76"/>
+      <c r="P9" s="77"/>
+      <c r="Q9" s="77"/>
+      <c r="R9" s="77"/>
+      <c r="S9" s="77"/>
+      <c r="T9" s="76"/>
+      <c r="U9" s="76"/>
+      <c r="V9" s="76"/>
+      <c r="W9" s="76"/>
+      <c r="X9" s="76"/>
+      <c r="Y9" s="76"/>
+      <c r="Z9" s="76"/>
+      <c r="AA9" s="76"/>
+      <c r="AB9" s="76"/>
+      <c r="AC9" s="76"/>
+      <c r="AD9" s="76"/>
+      <c r="AE9" s="76"/>
+      <c r="AF9" s="76"/>
+      <c r="AG9" s="76"/>
+      <c r="AH9" s="76"/>
+      <c r="AI9" s="76"/>
+      <c r="AJ9" s="76"/>
+      <c r="AK9" s="76"/>
+      <c r="AL9" s="76"/>
+      <c r="AM9" s="76"/>
+      <c r="AN9" s="76"/>
+      <c r="AO9" s="78"/>
+      <c r="AP9" s="76"/>
+      <c r="AQ9" s="76"/>
+      <c r="AR9" s="78"/>
+      <c r="AS9" s="76"/>
+      <c r="AT9" s="76"/>
+      <c r="AU9" s="76"/>
+      <c r="AV9" s="79"/>
+      <c r="AW9" s="76"/>
+      <c r="AX9" s="76"/>
+      <c r="AY9" s="76"/>
+      <c r="AZ9" s="76"/>
+      <c r="BA9" s="76"/>
+      <c r="BB9" s="76"/>
+      <c r="BC9" s="79"/>
+      <c r="BD9" s="76"/>
+      <c r="BE9" s="76"/>
+      <c r="BF9" s="76"/>
+      <c r="BG9" s="76"/>
+      <c r="BH9" s="76"/>
+      <c r="BI9" s="80"/>
+      <c r="BJ9" s="81"/>
+      <c r="BK9" s="65"/>
+      <c r="BL9" s="66"/>
+      <c r="BM9" s="67"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
@@ -4744,71 +5130,75 @@
       <c r="F10" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="G10" s="65" t="n">
+      <c r="G10" s="68" t="n">
         <f aca="false">Netzplan!J9</f>
         <v>2</v>
       </c>
-      <c r="H10" s="66" t="n">
+      <c r="H10" s="69" t="n">
         <f aca="false">SUM(I10:BJ10)</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="71"/>
-      <c r="J10" s="71"/>
-      <c r="K10" s="71"/>
-      <c r="L10" s="71"/>
-      <c r="M10" s="71"/>
-      <c r="N10" s="71"/>
-      <c r="O10" s="71"/>
-      <c r="P10" s="71"/>
-      <c r="Q10" s="71"/>
-      <c r="R10" s="71"/>
-      <c r="S10" s="71"/>
-      <c r="T10" s="72"/>
-      <c r="U10" s="71"/>
-      <c r="V10" s="71"/>
-      <c r="W10" s="72"/>
-      <c r="X10" s="72"/>
-      <c r="Y10" s="72"/>
-      <c r="Z10" s="72"/>
-      <c r="AA10" s="74"/>
-      <c r="AB10" s="71"/>
-      <c r="AC10" s="71"/>
-      <c r="AD10" s="72"/>
-      <c r="AE10" s="71"/>
-      <c r="AF10" s="71"/>
-      <c r="AG10" s="71"/>
-      <c r="AH10" s="71"/>
-      <c r="AI10" s="71"/>
-      <c r="AJ10" s="71"/>
-      <c r="AK10" s="71"/>
-      <c r="AL10" s="71"/>
-      <c r="AM10" s="71"/>
-      <c r="AN10" s="71"/>
-      <c r="AO10" s="71"/>
-      <c r="AP10" s="71"/>
-      <c r="AQ10" s="71"/>
-      <c r="AR10" s="71"/>
-      <c r="AS10" s="71"/>
-      <c r="AT10" s="71"/>
-      <c r="AU10" s="71"/>
-      <c r="AV10" s="73"/>
-      <c r="AW10" s="71"/>
-      <c r="AX10" s="71"/>
-      <c r="AY10" s="71"/>
-      <c r="AZ10" s="71"/>
-      <c r="BA10" s="71"/>
-      <c r="BB10" s="71"/>
-      <c r="BC10" s="73"/>
-      <c r="BD10" s="71"/>
-      <c r="BE10" s="71"/>
-      <c r="BF10" s="71"/>
-      <c r="BG10" s="71"/>
-      <c r="BH10" s="71"/>
-      <c r="BI10" s="73"/>
-      <c r="BJ10" s="74"/>
-      <c r="BK10" s="62"/>
-      <c r="BL10" s="63"/>
-      <c r="BM10" s="64"/>
+        <v>2</v>
+      </c>
+      <c r="I10" s="76"/>
+      <c r="J10" s="76"/>
+      <c r="K10" s="76"/>
+      <c r="L10" s="76"/>
+      <c r="M10" s="76"/>
+      <c r="N10" s="76"/>
+      <c r="O10" s="76"/>
+      <c r="P10" s="76"/>
+      <c r="Q10" s="76"/>
+      <c r="R10" s="76"/>
+      <c r="S10" s="76"/>
+      <c r="T10" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" s="76"/>
+      <c r="V10" s="76"/>
+      <c r="W10" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" s="77"/>
+      <c r="Y10" s="77"/>
+      <c r="Z10" s="77"/>
+      <c r="AA10" s="81"/>
+      <c r="AB10" s="76"/>
+      <c r="AC10" s="76"/>
+      <c r="AD10" s="77"/>
+      <c r="AE10" s="76"/>
+      <c r="AF10" s="76"/>
+      <c r="AG10" s="76"/>
+      <c r="AH10" s="76"/>
+      <c r="AI10" s="76"/>
+      <c r="AJ10" s="76"/>
+      <c r="AK10" s="76"/>
+      <c r="AL10" s="76"/>
+      <c r="AM10" s="76"/>
+      <c r="AN10" s="76"/>
+      <c r="AO10" s="78"/>
+      <c r="AP10" s="76"/>
+      <c r="AQ10" s="76"/>
+      <c r="AR10" s="78"/>
+      <c r="AS10" s="76"/>
+      <c r="AT10" s="76"/>
+      <c r="AU10" s="76"/>
+      <c r="AV10" s="79"/>
+      <c r="AW10" s="76"/>
+      <c r="AX10" s="76"/>
+      <c r="AY10" s="76"/>
+      <c r="AZ10" s="76"/>
+      <c r="BA10" s="76"/>
+      <c r="BB10" s="76"/>
+      <c r="BC10" s="79"/>
+      <c r="BD10" s="76"/>
+      <c r="BE10" s="76"/>
+      <c r="BF10" s="76"/>
+      <c r="BG10" s="76"/>
+      <c r="BH10" s="76"/>
+      <c r="BI10" s="80"/>
+      <c r="BJ10" s="81"/>
+      <c r="BK10" s="65"/>
+      <c r="BL10" s="66"/>
+      <c r="BM10" s="67"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
@@ -4825,70 +5215,74 @@
       <c r="F11" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="G11" s="65" t="n">
+      <c r="G11" s="68" t="n">
         <f aca="false">Netzplan!J10</f>
         <v>2</v>
       </c>
-      <c r="H11" s="66" t="n">
+      <c r="H11" s="69" t="n">
         <f aca="false">SUM(I11:BJ11)</f>
-        <v>0</v>
-      </c>
-      <c r="I11" s="71"/>
-      <c r="J11" s="71"/>
-      <c r="K11" s="71"/>
-      <c r="L11" s="71"/>
-      <c r="M11" s="71"/>
-      <c r="N11" s="71"/>
-      <c r="O11" s="71"/>
-      <c r="P11" s="71"/>
-      <c r="Q11" s="71"/>
-      <c r="R11" s="71"/>
-      <c r="S11" s="71"/>
-      <c r="T11" s="71"/>
-      <c r="U11" s="71"/>
-      <c r="V11" s="71"/>
-      <c r="W11" s="71"/>
-      <c r="X11" s="72"/>
-      <c r="Y11" s="72"/>
-      <c r="Z11" s="71"/>
-      <c r="AA11" s="71"/>
-      <c r="AB11" s="71"/>
-      <c r="AC11" s="71"/>
-      <c r="AE11" s="74"/>
-      <c r="AF11" s="71"/>
-      <c r="AG11" s="71"/>
-      <c r="AH11" s="71"/>
-      <c r="AI11" s="71"/>
-      <c r="AJ11" s="71"/>
-      <c r="AK11" s="71"/>
-      <c r="AL11" s="71"/>
-      <c r="AM11" s="71"/>
-      <c r="AN11" s="71"/>
-      <c r="AO11" s="71"/>
-      <c r="AP11" s="71"/>
-      <c r="AQ11" s="71"/>
-      <c r="AR11" s="71"/>
-      <c r="AS11" s="71"/>
-      <c r="AT11" s="71"/>
-      <c r="AU11" s="71"/>
-      <c r="AV11" s="73"/>
-      <c r="AW11" s="71"/>
-      <c r="AX11" s="71"/>
-      <c r="AY11" s="71"/>
-      <c r="AZ11" s="71"/>
-      <c r="BA11" s="71"/>
-      <c r="BB11" s="71"/>
-      <c r="BC11" s="73"/>
-      <c r="BD11" s="71"/>
-      <c r="BE11" s="71"/>
-      <c r="BF11" s="71"/>
-      <c r="BG11" s="71"/>
-      <c r="BH11" s="71"/>
-      <c r="BI11" s="73"/>
-      <c r="BJ11" s="74"/>
-      <c r="BK11" s="62"/>
-      <c r="BL11" s="63"/>
-      <c r="BM11" s="64"/>
+        <v>2</v>
+      </c>
+      <c r="I11" s="76"/>
+      <c r="J11" s="76"/>
+      <c r="K11" s="76"/>
+      <c r="L11" s="76"/>
+      <c r="M11" s="76"/>
+      <c r="N11" s="76"/>
+      <c r="O11" s="76"/>
+      <c r="P11" s="76"/>
+      <c r="Q11" s="76"/>
+      <c r="R11" s="76"/>
+      <c r="S11" s="76"/>
+      <c r="T11" s="76"/>
+      <c r="U11" s="76"/>
+      <c r="V11" s="76"/>
+      <c r="W11" s="76"/>
+      <c r="X11" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="76"/>
+      <c r="AA11" s="76"/>
+      <c r="AB11" s="76"/>
+      <c r="AC11" s="76"/>
+      <c r="AE11" s="81"/>
+      <c r="AF11" s="76"/>
+      <c r="AG11" s="76"/>
+      <c r="AH11" s="76"/>
+      <c r="AI11" s="76"/>
+      <c r="AJ11" s="76"/>
+      <c r="AK11" s="76"/>
+      <c r="AL11" s="76"/>
+      <c r="AM11" s="76"/>
+      <c r="AN11" s="76"/>
+      <c r="AO11" s="78"/>
+      <c r="AP11" s="76"/>
+      <c r="AQ11" s="76"/>
+      <c r="AR11" s="78"/>
+      <c r="AS11" s="76"/>
+      <c r="AT11" s="76"/>
+      <c r="AU11" s="76"/>
+      <c r="AV11" s="79"/>
+      <c r="AW11" s="76"/>
+      <c r="AX11" s="76"/>
+      <c r="AY11" s="76"/>
+      <c r="AZ11" s="76"/>
+      <c r="BA11" s="76"/>
+      <c r="BB11" s="76"/>
+      <c r="BC11" s="79"/>
+      <c r="BD11" s="76"/>
+      <c r="BE11" s="76"/>
+      <c r="BF11" s="76"/>
+      <c r="BG11" s="76"/>
+      <c r="BH11" s="76"/>
+      <c r="BI11" s="80"/>
+      <c r="BJ11" s="81"/>
+      <c r="BK11" s="65"/>
+      <c r="BL11" s="66"/>
+      <c r="BM11" s="67"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
@@ -4905,70 +5299,74 @@
       <c r="F12" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="G12" s="65" t="n">
+      <c r="G12" s="68" t="n">
         <f aca="false">Netzplan!J11</f>
         <v>2</v>
       </c>
-      <c r="H12" s="66" t="n">
+      <c r="H12" s="69" t="n">
         <f aca="false">SUM(I12:BJ12)</f>
-        <v>0</v>
-      </c>
-      <c r="I12" s="71"/>
-      <c r="J12" s="71"/>
-      <c r="K12" s="71"/>
-      <c r="L12" s="71"/>
-      <c r="M12" s="71"/>
-      <c r="N12" s="71"/>
-      <c r="O12" s="71"/>
-      <c r="P12" s="71"/>
-      <c r="Q12" s="71"/>
-      <c r="R12" s="71"/>
-      <c r="S12" s="71"/>
-      <c r="T12" s="71"/>
-      <c r="U12" s="71"/>
-      <c r="V12" s="71"/>
-      <c r="W12" s="71"/>
-      <c r="X12" s="71"/>
-      <c r="Y12" s="71"/>
-      <c r="Z12" s="72"/>
-      <c r="AA12" s="72"/>
-      <c r="AB12" s="71"/>
-      <c r="AC12" s="71"/>
-      <c r="AE12" s="74"/>
-      <c r="AF12" s="71"/>
-      <c r="AG12" s="72"/>
-      <c r="AH12" s="72"/>
-      <c r="AI12" s="71"/>
-      <c r="AJ12" s="71"/>
-      <c r="AK12" s="71"/>
-      <c r="AL12" s="71"/>
-      <c r="AM12" s="71"/>
-      <c r="AN12" s="71"/>
-      <c r="AO12" s="71"/>
-      <c r="AP12" s="71"/>
-      <c r="AQ12" s="71"/>
-      <c r="AR12" s="71"/>
-      <c r="AS12" s="71"/>
-      <c r="AT12" s="71"/>
-      <c r="AU12" s="71"/>
-      <c r="AV12" s="73"/>
-      <c r="AW12" s="71"/>
-      <c r="AX12" s="71"/>
-      <c r="AY12" s="71"/>
-      <c r="AZ12" s="71"/>
-      <c r="BA12" s="71"/>
-      <c r="BB12" s="71"/>
-      <c r="BC12" s="73"/>
-      <c r="BD12" s="71"/>
-      <c r="BE12" s="71"/>
-      <c r="BF12" s="71"/>
-      <c r="BG12" s="71"/>
-      <c r="BH12" s="71"/>
-      <c r="BI12" s="73"/>
-      <c r="BJ12" s="74"/>
-      <c r="BK12" s="62"/>
-      <c r="BL12" s="63"/>
-      <c r="BM12" s="64"/>
+        <v>2</v>
+      </c>
+      <c r="I12" s="76"/>
+      <c r="J12" s="76"/>
+      <c r="K12" s="76"/>
+      <c r="L12" s="76"/>
+      <c r="M12" s="76"/>
+      <c r="N12" s="76"/>
+      <c r="O12" s="76"/>
+      <c r="P12" s="76"/>
+      <c r="Q12" s="76"/>
+      <c r="R12" s="76"/>
+      <c r="S12" s="76"/>
+      <c r="T12" s="76"/>
+      <c r="U12" s="76"/>
+      <c r="V12" s="76"/>
+      <c r="W12" s="76"/>
+      <c r="X12" s="76"/>
+      <c r="Y12" s="76"/>
+      <c r="Z12" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="76"/>
+      <c r="AC12" s="76"/>
+      <c r="AE12" s="81"/>
+      <c r="AF12" s="76"/>
+      <c r="AG12" s="77"/>
+      <c r="AH12" s="77"/>
+      <c r="AI12" s="76"/>
+      <c r="AJ12" s="76"/>
+      <c r="AK12" s="76"/>
+      <c r="AL12" s="76"/>
+      <c r="AM12" s="76"/>
+      <c r="AN12" s="76"/>
+      <c r="AO12" s="78"/>
+      <c r="AP12" s="76"/>
+      <c r="AQ12" s="76"/>
+      <c r="AR12" s="78"/>
+      <c r="AS12" s="76"/>
+      <c r="AT12" s="76"/>
+      <c r="AU12" s="76"/>
+      <c r="AV12" s="79"/>
+      <c r="AW12" s="76"/>
+      <c r="AX12" s="76"/>
+      <c r="AY12" s="76"/>
+      <c r="AZ12" s="76"/>
+      <c r="BA12" s="76"/>
+      <c r="BB12" s="76"/>
+      <c r="BC12" s="79"/>
+      <c r="BD12" s="76"/>
+      <c r="BE12" s="76"/>
+      <c r="BF12" s="76"/>
+      <c r="BG12" s="76"/>
+      <c r="BH12" s="76"/>
+      <c r="BI12" s="80"/>
+      <c r="BJ12" s="81"/>
+      <c r="BK12" s="65"/>
+      <c r="BL12" s="66"/>
+      <c r="BM12" s="67"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
@@ -4985,71 +5383,111 @@
       <c r="F13" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="G13" s="65" t="n">
+      <c r="G13" s="68" t="n">
         <f aca="false">Netzplan!J12</f>
         <v>20</v>
       </c>
-      <c r="H13" s="66" t="n">
+      <c r="H13" s="69" t="n">
         <f aca="false">SUM(I13:BJ13)</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="71"/>
-      <c r="J13" s="71"/>
-      <c r="K13" s="71"/>
-      <c r="L13" s="71"/>
-      <c r="M13" s="71"/>
-      <c r="N13" s="71"/>
-      <c r="O13" s="71"/>
-      <c r="P13" s="71"/>
-      <c r="Q13" s="71"/>
-      <c r="R13" s="71"/>
-      <c r="S13" s="71"/>
-      <c r="T13" s="72"/>
-      <c r="U13" s="71"/>
-      <c r="V13" s="71"/>
-      <c r="W13" s="72"/>
-      <c r="X13" s="72"/>
-      <c r="Y13" s="72"/>
-      <c r="Z13" s="72"/>
-      <c r="AA13" s="72"/>
-      <c r="AB13" s="71"/>
-      <c r="AC13" s="71"/>
-      <c r="AD13" s="72"/>
-      <c r="AE13" s="72"/>
-      <c r="AF13" s="72"/>
-      <c r="AG13" s="72"/>
-      <c r="AH13" s="72"/>
-      <c r="AI13" s="71"/>
-      <c r="AJ13" s="71"/>
-      <c r="AK13" s="72"/>
-      <c r="AL13" s="72"/>
-      <c r="AM13" s="72"/>
-      <c r="AN13" s="72"/>
-      <c r="AO13" s="72"/>
-      <c r="AP13" s="71"/>
-      <c r="AQ13" s="71"/>
-      <c r="AR13" s="72"/>
-      <c r="AS13" s="72"/>
-      <c r="AT13" s="72"/>
-      <c r="AU13" s="72"/>
-      <c r="AV13" s="76"/>
-      <c r="AW13" s="71"/>
-      <c r="AX13" s="71"/>
-      <c r="AY13" s="72"/>
-      <c r="AZ13" s="72"/>
-      <c r="BA13" s="72"/>
-      <c r="BB13" s="72"/>
-      <c r="BC13" s="73"/>
-      <c r="BD13" s="71"/>
-      <c r="BE13" s="71"/>
-      <c r="BF13" s="71"/>
-      <c r="BG13" s="71"/>
-      <c r="BH13" s="71"/>
-      <c r="BI13" s="73"/>
-      <c r="BJ13" s="74"/>
-      <c r="BK13" s="62"/>
-      <c r="BL13" s="63"/>
-      <c r="BM13" s="64"/>
+        <v>20</v>
+      </c>
+      <c r="I13" s="76"/>
+      <c r="J13" s="76"/>
+      <c r="K13" s="76"/>
+      <c r="L13" s="76"/>
+      <c r="M13" s="76"/>
+      <c r="N13" s="76"/>
+      <c r="O13" s="76"/>
+      <c r="P13" s="76"/>
+      <c r="Q13" s="76"/>
+      <c r="R13" s="76"/>
+      <c r="S13" s="76"/>
+      <c r="T13" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" s="76"/>
+      <c r="V13" s="76"/>
+      <c r="W13" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB13" s="76"/>
+      <c r="AC13" s="76"/>
+      <c r="AD13" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE13" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG13" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH13" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI13" s="76"/>
+      <c r="AJ13" s="76"/>
+      <c r="AK13" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL13" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM13" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN13" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO13" s="83"/>
+      <c r="AP13" s="76"/>
+      <c r="AQ13" s="76"/>
+      <c r="AR13" s="83"/>
+      <c r="AS13" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT13" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV13" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW13" s="76"/>
+      <c r="AX13" s="76"/>
+      <c r="AY13" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ13" s="77"/>
+      <c r="BA13" s="77"/>
+      <c r="BB13" s="77"/>
+      <c r="BC13" s="79"/>
+      <c r="BD13" s="76"/>
+      <c r="BE13" s="76"/>
+      <c r="BF13" s="76"/>
+      <c r="BG13" s="76"/>
+      <c r="BH13" s="76"/>
+      <c r="BI13" s="80"/>
+      <c r="BJ13" s="81"/>
+      <c r="BK13" s="65"/>
+      <c r="BL13" s="66"/>
+      <c r="BM13" s="67"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14"/>
@@ -5060,65 +5498,65 @@
       <c r="D14" s="42"/>
       <c r="E14" s="41"/>
       <c r="F14" s="41"/>
-      <c r="G14" s="65"/>
-      <c r="H14" s="66"/>
-      <c r="I14" s="71"/>
-      <c r="J14" s="71"/>
-      <c r="K14" s="71"/>
-      <c r="L14" s="71"/>
-      <c r="M14" s="71"/>
-      <c r="N14" s="71"/>
-      <c r="O14" s="71"/>
-      <c r="P14" s="71"/>
-      <c r="Q14" s="71"/>
-      <c r="R14" s="71"/>
-      <c r="S14" s="71"/>
-      <c r="T14" s="72"/>
-      <c r="U14" s="71"/>
-      <c r="V14" s="71"/>
-      <c r="W14" s="72"/>
-      <c r="X14" s="72"/>
-      <c r="Y14" s="72"/>
-      <c r="Z14" s="72"/>
-      <c r="AA14" s="72"/>
-      <c r="AB14" s="71"/>
-      <c r="AC14" s="71"/>
-      <c r="AD14" s="72"/>
-      <c r="AE14" s="72"/>
-      <c r="AF14" s="72"/>
-      <c r="AG14" s="72"/>
-      <c r="AH14" s="72"/>
-      <c r="AI14" s="71"/>
-      <c r="AJ14" s="71"/>
-      <c r="AK14" s="72"/>
-      <c r="AL14" s="72"/>
-      <c r="AM14" s="72"/>
-      <c r="AN14" s="72"/>
-      <c r="AO14" s="72"/>
-      <c r="AP14" s="71"/>
-      <c r="AQ14" s="71"/>
-      <c r="AR14" s="72"/>
-      <c r="AS14" s="72"/>
-      <c r="AT14" s="72"/>
-      <c r="AU14" s="72"/>
-      <c r="AV14" s="76"/>
-      <c r="AW14" s="71"/>
-      <c r="AX14" s="71"/>
-      <c r="AY14" s="72"/>
-      <c r="AZ14" s="72"/>
-      <c r="BA14" s="72"/>
-      <c r="BB14" s="72"/>
-      <c r="BC14" s="73"/>
-      <c r="BD14" s="71"/>
-      <c r="BE14" s="71"/>
-      <c r="BF14" s="71"/>
-      <c r="BG14" s="71"/>
-      <c r="BH14" s="71"/>
-      <c r="BI14" s="73"/>
-      <c r="BJ14" s="74"/>
-      <c r="BK14" s="62"/>
-      <c r="BL14" s="63"/>
-      <c r="BM14" s="64"/>
+      <c r="G14" s="68"/>
+      <c r="H14" s="69"/>
+      <c r="I14" s="76"/>
+      <c r="J14" s="76"/>
+      <c r="K14" s="76"/>
+      <c r="L14" s="76"/>
+      <c r="M14" s="76"/>
+      <c r="N14" s="76"/>
+      <c r="O14" s="76"/>
+      <c r="P14" s="76"/>
+      <c r="Q14" s="76"/>
+      <c r="R14" s="76"/>
+      <c r="S14" s="76"/>
+      <c r="T14" s="77"/>
+      <c r="U14" s="76"/>
+      <c r="V14" s="76"/>
+      <c r="W14" s="77"/>
+      <c r="X14" s="77"/>
+      <c r="Y14" s="77"/>
+      <c r="Z14" s="77"/>
+      <c r="AA14" s="77"/>
+      <c r="AB14" s="76"/>
+      <c r="AC14" s="76"/>
+      <c r="AD14" s="77"/>
+      <c r="AE14" s="77"/>
+      <c r="AF14" s="77"/>
+      <c r="AG14" s="77"/>
+      <c r="AH14" s="77"/>
+      <c r="AI14" s="76"/>
+      <c r="AJ14" s="76"/>
+      <c r="AK14" s="77"/>
+      <c r="AL14" s="77"/>
+      <c r="AM14" s="77"/>
+      <c r="AN14" s="77"/>
+      <c r="AO14" s="83"/>
+      <c r="AP14" s="76"/>
+      <c r="AQ14" s="76"/>
+      <c r="AR14" s="83"/>
+      <c r="AS14" s="77"/>
+      <c r="AT14" s="77"/>
+      <c r="AU14" s="77"/>
+      <c r="AV14" s="77"/>
+      <c r="AW14" s="76"/>
+      <c r="AX14" s="76"/>
+      <c r="AY14" s="77"/>
+      <c r="AZ14" s="77"/>
+      <c r="BA14" s="77"/>
+      <c r="BB14" s="77"/>
+      <c r="BC14" s="79"/>
+      <c r="BD14" s="76"/>
+      <c r="BE14" s="76"/>
+      <c r="BF14" s="76"/>
+      <c r="BG14" s="76"/>
+      <c r="BH14" s="76"/>
+      <c r="BI14" s="80"/>
+      <c r="BJ14" s="81"/>
+      <c r="BK14" s="65"/>
+      <c r="BL14" s="66"/>
+      <c r="BM14" s="67"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
@@ -5135,70 +5573,74 @@
       <c r="F15" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="G15" s="65" t="n">
+      <c r="G15" s="68" t="n">
         <f aca="false">Netzplan!J13</f>
         <v>2</v>
       </c>
-      <c r="H15" s="66" t="n">
+      <c r="H15" s="69" t="n">
         <f aca="false">SUM(I15:BJ15)</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="71"/>
-      <c r="J15" s="71"/>
-      <c r="K15" s="71"/>
-      <c r="L15" s="71"/>
-      <c r="M15" s="71"/>
-      <c r="N15" s="71"/>
-      <c r="O15" s="71"/>
-      <c r="P15" s="71"/>
-      <c r="Q15" s="71"/>
-      <c r="R15" s="71"/>
-      <c r="S15" s="71"/>
-      <c r="T15" s="71"/>
-      <c r="U15" s="71"/>
-      <c r="V15" s="71"/>
-      <c r="W15" s="71"/>
-      <c r="X15" s="71"/>
-      <c r="Y15" s="71"/>
-      <c r="Z15" s="71"/>
-      <c r="AA15" s="71"/>
-      <c r="AB15" s="71"/>
-      <c r="AC15" s="71"/>
-      <c r="AE15" s="72"/>
-      <c r="AF15" s="72"/>
-      <c r="AG15" s="71"/>
-      <c r="AH15" s="71"/>
-      <c r="AI15" s="71"/>
-      <c r="AJ15" s="71"/>
-      <c r="AK15" s="72"/>
-      <c r="AL15" s="72"/>
-      <c r="AM15" s="72"/>
-      <c r="AN15" s="72"/>
-      <c r="AO15" s="72"/>
-      <c r="AP15" s="71"/>
-      <c r="AQ15" s="71"/>
-      <c r="AR15" s="71"/>
-      <c r="AS15" s="71"/>
-      <c r="AT15" s="71"/>
-      <c r="AU15" s="71"/>
-      <c r="AV15" s="73"/>
-      <c r="AW15" s="71"/>
-      <c r="AX15" s="71"/>
-      <c r="AY15" s="71"/>
-      <c r="AZ15" s="71"/>
-      <c r="BA15" s="71"/>
-      <c r="BB15" s="71"/>
-      <c r="BC15" s="73"/>
-      <c r="BD15" s="71"/>
-      <c r="BE15" s="71"/>
-      <c r="BF15" s="71"/>
-      <c r="BG15" s="71"/>
-      <c r="BH15" s="71"/>
-      <c r="BI15" s="73"/>
-      <c r="BJ15" s="74"/>
-      <c r="BK15" s="62"/>
-      <c r="BL15" s="63"/>
-      <c r="BM15" s="64"/>
+        <v>2</v>
+      </c>
+      <c r="I15" s="76"/>
+      <c r="J15" s="76"/>
+      <c r="K15" s="76"/>
+      <c r="L15" s="76"/>
+      <c r="M15" s="76"/>
+      <c r="N15" s="76"/>
+      <c r="O15" s="76"/>
+      <c r="P15" s="76"/>
+      <c r="Q15" s="76"/>
+      <c r="R15" s="76"/>
+      <c r="S15" s="76"/>
+      <c r="T15" s="76"/>
+      <c r="U15" s="76"/>
+      <c r="V15" s="76"/>
+      <c r="W15" s="76"/>
+      <c r="X15" s="76"/>
+      <c r="Y15" s="76"/>
+      <c r="Z15" s="76"/>
+      <c r="AA15" s="76"/>
+      <c r="AB15" s="76"/>
+      <c r="AC15" s="76"/>
+      <c r="AE15" s="84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF15" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG15" s="76"/>
+      <c r="AH15" s="76"/>
+      <c r="AI15" s="76"/>
+      <c r="AJ15" s="76"/>
+      <c r="AK15" s="77"/>
+      <c r="AL15" s="77"/>
+      <c r="AM15" s="77"/>
+      <c r="AN15" s="77"/>
+      <c r="AO15" s="83"/>
+      <c r="AP15" s="76"/>
+      <c r="AQ15" s="76"/>
+      <c r="AR15" s="78"/>
+      <c r="AS15" s="76"/>
+      <c r="AT15" s="76"/>
+      <c r="AU15" s="76"/>
+      <c r="AV15" s="79"/>
+      <c r="AW15" s="76"/>
+      <c r="AX15" s="76"/>
+      <c r="AY15" s="76"/>
+      <c r="AZ15" s="76"/>
+      <c r="BA15" s="76"/>
+      <c r="BB15" s="76"/>
+      <c r="BC15" s="79"/>
+      <c r="BD15" s="76"/>
+      <c r="BE15" s="76"/>
+      <c r="BF15" s="76"/>
+      <c r="BG15" s="76"/>
+      <c r="BH15" s="76"/>
+      <c r="BI15" s="80"/>
+      <c r="BJ15" s="81"/>
+      <c r="BK15" s="65"/>
+      <c r="BL15" s="66"/>
+      <c r="BM15" s="67"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
@@ -5215,69 +5657,73 @@
       <c r="F16" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="G16" s="65" t="n">
+      <c r="G16" s="68" t="n">
         <f aca="false">Netzplan!J14</f>
         <v>2</v>
       </c>
-      <c r="H16" s="66" t="n">
+      <c r="H16" s="69" t="n">
         <f aca="false">SUM(I16:BJ16)</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="71"/>
-      <c r="J16" s="71"/>
-      <c r="K16" s="71"/>
-      <c r="L16" s="71"/>
-      <c r="M16" s="71"/>
-      <c r="N16" s="71"/>
-      <c r="O16" s="71"/>
-      <c r="P16" s="71"/>
-      <c r="Q16" s="71"/>
-      <c r="R16" s="71"/>
-      <c r="S16" s="71"/>
-      <c r="T16" s="71"/>
-      <c r="U16" s="71"/>
-      <c r="V16" s="71"/>
-      <c r="W16" s="71"/>
-      <c r="X16" s="71"/>
-      <c r="Y16" s="71"/>
-      <c r="Z16" s="71"/>
-      <c r="AA16" s="71"/>
-      <c r="AB16" s="71"/>
-      <c r="AC16" s="71"/>
-      <c r="AD16" s="71"/>
-      <c r="AE16" s="71"/>
-      <c r="AG16" s="71"/>
-      <c r="AH16" s="71"/>
-      <c r="AI16" s="71"/>
-      <c r="AJ16" s="71"/>
-      <c r="AL16" s="71"/>
-      <c r="AM16" s="71"/>
-      <c r="AN16" s="71"/>
-      <c r="AO16" s="72"/>
-      <c r="AP16" s="71"/>
-      <c r="AQ16" s="71"/>
-      <c r="AR16" s="72"/>
-      <c r="AS16" s="72"/>
-      <c r="AT16" s="72"/>
-      <c r="AU16" s="71"/>
-      <c r="AV16" s="73"/>
-      <c r="AW16" s="71"/>
-      <c r="AX16" s="71"/>
-      <c r="AY16" s="71"/>
-      <c r="AZ16" s="71"/>
-      <c r="BA16" s="71"/>
-      <c r="BB16" s="71"/>
-      <c r="BC16" s="73"/>
-      <c r="BD16" s="71"/>
-      <c r="BE16" s="71"/>
-      <c r="BF16" s="71"/>
-      <c r="BG16" s="71"/>
-      <c r="BH16" s="71"/>
-      <c r="BI16" s="73"/>
-      <c r="BJ16" s="74"/>
-      <c r="BK16" s="62"/>
-      <c r="BL16" s="63"/>
-      <c r="BM16" s="64"/>
+        <v>2</v>
+      </c>
+      <c r="I16" s="76"/>
+      <c r="J16" s="76"/>
+      <c r="K16" s="76"/>
+      <c r="L16" s="76"/>
+      <c r="M16" s="76"/>
+      <c r="N16" s="76"/>
+      <c r="O16" s="76"/>
+      <c r="P16" s="76"/>
+      <c r="Q16" s="76"/>
+      <c r="R16" s="76"/>
+      <c r="S16" s="76"/>
+      <c r="T16" s="76"/>
+      <c r="U16" s="76"/>
+      <c r="V16" s="76"/>
+      <c r="W16" s="76"/>
+      <c r="X16" s="76"/>
+      <c r="Y16" s="76"/>
+      <c r="Z16" s="76"/>
+      <c r="AA16" s="76"/>
+      <c r="AB16" s="76"/>
+      <c r="AC16" s="76"/>
+      <c r="AD16" s="76"/>
+      <c r="AE16" s="76"/>
+      <c r="AG16" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH16" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI16" s="76"/>
+      <c r="AJ16" s="76"/>
+      <c r="AL16" s="76"/>
+      <c r="AM16" s="76"/>
+      <c r="AN16" s="76"/>
+      <c r="AO16" s="83"/>
+      <c r="AP16" s="76"/>
+      <c r="AQ16" s="76"/>
+      <c r="AR16" s="83"/>
+      <c r="AS16" s="77"/>
+      <c r="AT16" s="77"/>
+      <c r="AU16" s="76"/>
+      <c r="AV16" s="79"/>
+      <c r="AW16" s="76"/>
+      <c r="AX16" s="76"/>
+      <c r="AY16" s="76"/>
+      <c r="AZ16" s="76"/>
+      <c r="BA16" s="76"/>
+      <c r="BB16" s="76"/>
+      <c r="BC16" s="79"/>
+      <c r="BD16" s="76"/>
+      <c r="BE16" s="76"/>
+      <c r="BF16" s="76"/>
+      <c r="BG16" s="76"/>
+      <c r="BH16" s="76"/>
+      <c r="BI16" s="80"/>
+      <c r="BJ16" s="81"/>
+      <c r="BK16" s="65"/>
+      <c r="BL16" s="66"/>
+      <c r="BM16" s="67"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
@@ -5294,68 +5740,70 @@
       <c r="F17" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="G17" s="65" t="n">
+      <c r="G17" s="68" t="n">
         <f aca="false">Netzplan!J15</f>
         <v>1</v>
       </c>
-      <c r="H17" s="66" t="n">
+      <c r="H17" s="69" t="n">
         <f aca="false">SUM(I17:BJ17)</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="71"/>
-      <c r="J17" s="71"/>
-      <c r="K17" s="71"/>
-      <c r="L17" s="71"/>
-      <c r="M17" s="71"/>
-      <c r="N17" s="71"/>
-      <c r="O17" s="71"/>
-      <c r="P17" s="71"/>
-      <c r="Q17" s="71"/>
-      <c r="R17" s="71"/>
-      <c r="S17" s="71"/>
-      <c r="T17" s="71"/>
-      <c r="U17" s="71"/>
-      <c r="V17" s="71"/>
-      <c r="W17" s="71"/>
-      <c r="X17" s="71"/>
-      <c r="Y17" s="71"/>
-      <c r="Z17" s="71"/>
-      <c r="AA17" s="71"/>
-      <c r="AB17" s="71"/>
-      <c r="AC17" s="71"/>
-      <c r="AD17" s="71"/>
-      <c r="AE17" s="71"/>
-      <c r="AF17" s="71"/>
-      <c r="AG17" s="71"/>
-      <c r="AI17" s="71"/>
-      <c r="AJ17" s="71"/>
-      <c r="AL17" s="71"/>
-      <c r="AM17" s="71"/>
-      <c r="AO17" s="71"/>
-      <c r="AP17" s="71"/>
-      <c r="AQ17" s="71"/>
-      <c r="AR17" s="74"/>
-      <c r="AS17" s="72"/>
-      <c r="AT17" s="71"/>
-      <c r="AU17" s="71"/>
-      <c r="AV17" s="73"/>
-      <c r="AW17" s="71"/>
-      <c r="AX17" s="71"/>
-      <c r="AY17" s="71"/>
-      <c r="AZ17" s="71"/>
-      <c r="BA17" s="71"/>
-      <c r="BB17" s="71"/>
-      <c r="BC17" s="73"/>
-      <c r="BD17" s="71"/>
-      <c r="BE17" s="71"/>
-      <c r="BF17" s="71"/>
-      <c r="BG17" s="71"/>
-      <c r="BH17" s="71"/>
-      <c r="BI17" s="73"/>
-      <c r="BJ17" s="74"/>
-      <c r="BK17" s="62"/>
-      <c r="BL17" s="63"/>
-      <c r="BM17" s="64"/>
+        <v>1</v>
+      </c>
+      <c r="I17" s="76"/>
+      <c r="J17" s="76"/>
+      <c r="K17" s="76"/>
+      <c r="L17" s="76"/>
+      <c r="M17" s="76"/>
+      <c r="N17" s="76"/>
+      <c r="O17" s="76"/>
+      <c r="P17" s="76"/>
+      <c r="Q17" s="76"/>
+      <c r="R17" s="76"/>
+      <c r="S17" s="76"/>
+      <c r="T17" s="76"/>
+      <c r="U17" s="76"/>
+      <c r="V17" s="76"/>
+      <c r="W17" s="76"/>
+      <c r="X17" s="76"/>
+      <c r="Y17" s="76"/>
+      <c r="Z17" s="76"/>
+      <c r="AA17" s="76"/>
+      <c r="AB17" s="76"/>
+      <c r="AC17" s="76"/>
+      <c r="AD17" s="76"/>
+      <c r="AE17" s="76"/>
+      <c r="AF17" s="76"/>
+      <c r="AG17" s="76"/>
+      <c r="AI17" s="76"/>
+      <c r="AJ17" s="76"/>
+      <c r="AL17" s="76"/>
+      <c r="AM17" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO17" s="78"/>
+      <c r="AP17" s="76"/>
+      <c r="AQ17" s="76"/>
+      <c r="AR17" s="85"/>
+      <c r="AS17" s="77"/>
+      <c r="AT17" s="76"/>
+      <c r="AU17" s="76"/>
+      <c r="AV17" s="79"/>
+      <c r="AW17" s="76"/>
+      <c r="AX17" s="76"/>
+      <c r="AY17" s="76"/>
+      <c r="AZ17" s="76"/>
+      <c r="BA17" s="76"/>
+      <c r="BB17" s="76"/>
+      <c r="BC17" s="79"/>
+      <c r="BD17" s="76"/>
+      <c r="BE17" s="76"/>
+      <c r="BF17" s="76"/>
+      <c r="BG17" s="76"/>
+      <c r="BH17" s="76"/>
+      <c r="BI17" s="80"/>
+      <c r="BJ17" s="81"/>
+      <c r="BK17" s="65"/>
+      <c r="BL17" s="66"/>
+      <c r="BM17" s="67"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
@@ -5372,70 +5820,76 @@
       <c r="F18" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="G18" s="65" t="n">
+      <c r="G18" s="68" t="n">
         <f aca="false">Netzplan!J16</f>
         <v>4</v>
       </c>
-      <c r="H18" s="66" t="n">
+      <c r="H18" s="69" t="n">
         <f aca="false">SUM(I18:BJ18)</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="71"/>
-      <c r="J18" s="71"/>
-      <c r="K18" s="71"/>
-      <c r="L18" s="71"/>
-      <c r="M18" s="71"/>
-      <c r="N18" s="71"/>
-      <c r="O18" s="71"/>
-      <c r="P18" s="71"/>
-      <c r="Q18" s="71"/>
-      <c r="R18" s="71"/>
-      <c r="S18" s="71"/>
-      <c r="T18" s="71"/>
-      <c r="U18" s="71"/>
-      <c r="V18" s="71"/>
-      <c r="W18" s="71"/>
-      <c r="X18" s="71"/>
-      <c r="Y18" s="71"/>
-      <c r="Z18" s="71"/>
-      <c r="AA18" s="71"/>
-      <c r="AB18" s="71"/>
-      <c r="AC18" s="71"/>
-      <c r="AD18" s="71"/>
-      <c r="AE18" s="71"/>
-      <c r="AF18" s="71"/>
-      <c r="AG18" s="71"/>
-      <c r="AH18" s="71"/>
-      <c r="AI18" s="71"/>
-      <c r="AJ18" s="71"/>
-      <c r="AL18" s="71"/>
-      <c r="AM18" s="74"/>
-      <c r="AN18" s="74"/>
-      <c r="AO18" s="71"/>
-      <c r="AP18" s="71"/>
-      <c r="AQ18" s="71"/>
-      <c r="AR18" s="71"/>
-      <c r="AS18" s="71"/>
-      <c r="AT18" s="71"/>
-      <c r="AU18" s="72"/>
-      <c r="AV18" s="73"/>
-      <c r="AW18" s="71"/>
-      <c r="AX18" s="71"/>
-      <c r="AY18" s="72"/>
-      <c r="AZ18" s="72"/>
-      <c r="BA18" s="72"/>
-      <c r="BB18" s="71"/>
-      <c r="BC18" s="73"/>
-      <c r="BD18" s="71"/>
-      <c r="BE18" s="71"/>
-      <c r="BF18" s="71"/>
-      <c r="BG18" s="71"/>
-      <c r="BH18" s="71"/>
-      <c r="BI18" s="73"/>
-      <c r="BJ18" s="74"/>
-      <c r="BK18" s="62"/>
-      <c r="BL18" s="63"/>
-      <c r="BM18" s="64"/>
+        <v>4</v>
+      </c>
+      <c r="I18" s="76"/>
+      <c r="J18" s="76"/>
+      <c r="K18" s="76"/>
+      <c r="L18" s="76"/>
+      <c r="M18" s="76"/>
+      <c r="N18" s="76"/>
+      <c r="O18" s="76"/>
+      <c r="P18" s="76"/>
+      <c r="Q18" s="76"/>
+      <c r="R18" s="76"/>
+      <c r="S18" s="76"/>
+      <c r="T18" s="76"/>
+      <c r="U18" s="76"/>
+      <c r="V18" s="76"/>
+      <c r="W18" s="76"/>
+      <c r="X18" s="76"/>
+      <c r="Y18" s="76"/>
+      <c r="Z18" s="76"/>
+      <c r="AA18" s="76"/>
+      <c r="AB18" s="76"/>
+      <c r="AC18" s="76"/>
+      <c r="AD18" s="76"/>
+      <c r="AE18" s="76"/>
+      <c r="AF18" s="76"/>
+      <c r="AG18" s="76"/>
+      <c r="AH18" s="76"/>
+      <c r="AI18" s="76"/>
+      <c r="AJ18" s="76"/>
+      <c r="AN18" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO18" s="78"/>
+      <c r="AP18" s="76"/>
+      <c r="AQ18" s="76"/>
+      <c r="AR18" s="78"/>
+      <c r="AS18" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT18" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU18" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV18" s="79"/>
+      <c r="AW18" s="76"/>
+      <c r="AX18" s="76"/>
+      <c r="AY18" s="77"/>
+      <c r="AZ18" s="77"/>
+      <c r="BA18" s="77"/>
+      <c r="BB18" s="76"/>
+      <c r="BC18" s="79"/>
+      <c r="BD18" s="76"/>
+      <c r="BE18" s="76"/>
+      <c r="BF18" s="76"/>
+      <c r="BG18" s="76"/>
+      <c r="BH18" s="76"/>
+      <c r="BI18" s="80"/>
+      <c r="BJ18" s="81"/>
+      <c r="BK18" s="65"/>
+      <c r="BL18" s="66"/>
+      <c r="BM18" s="67"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="17" t="s">
@@ -5450,71 +5904,73 @@
         <v>60</v>
       </c>
       <c r="F19" s="46"/>
-      <c r="G19" s="65" t="n">
+      <c r="G19" s="68" t="n">
         <f aca="false">Netzplan!J17</f>
         <v>1</v>
       </c>
-      <c r="H19" s="66" t="n">
+      <c r="H19" s="69" t="n">
         <f aca="false">SUM(I19:BJ19)</f>
-        <v>0</v>
-      </c>
-      <c r="I19" s="77"/>
-      <c r="J19" s="77"/>
-      <c r="K19" s="77"/>
-      <c r="L19" s="77"/>
-      <c r="M19" s="77"/>
-      <c r="N19" s="77"/>
-      <c r="O19" s="77"/>
-      <c r="P19" s="77"/>
-      <c r="Q19" s="77"/>
-      <c r="R19" s="77"/>
-      <c r="S19" s="77"/>
-      <c r="T19" s="77"/>
-      <c r="U19" s="77"/>
-      <c r="V19" s="77"/>
-      <c r="W19" s="77"/>
-      <c r="X19" s="77"/>
-      <c r="Y19" s="77"/>
-      <c r="Z19" s="77"/>
-      <c r="AA19" s="77"/>
-      <c r="AB19" s="77"/>
-      <c r="AC19" s="77"/>
-      <c r="AD19" s="77"/>
-      <c r="AE19" s="77"/>
-      <c r="AF19" s="77"/>
-      <c r="AG19" s="77"/>
-      <c r="AH19" s="77"/>
-      <c r="AI19" s="77"/>
-      <c r="AJ19" s="77"/>
-      <c r="AK19" s="77"/>
-      <c r="AL19" s="77"/>
-      <c r="AM19" s="77"/>
-      <c r="AN19" s="77"/>
-      <c r="AO19" s="77"/>
-      <c r="AP19" s="77"/>
-      <c r="AQ19" s="77"/>
-      <c r="AR19" s="77"/>
-      <c r="AS19" s="77"/>
-      <c r="AT19" s="77"/>
-      <c r="AU19" s="77"/>
-      <c r="AV19" s="78"/>
-      <c r="AW19" s="77"/>
-      <c r="AX19" s="77"/>
-      <c r="AY19" s="79"/>
-      <c r="AZ19" s="79"/>
-      <c r="BA19" s="77"/>
-      <c r="BB19" s="77"/>
-      <c r="BC19" s="78"/>
-      <c r="BD19" s="77"/>
-      <c r="BE19" s="77"/>
-      <c r="BF19" s="77"/>
-      <c r="BG19" s="77"/>
-      <c r="BH19" s="77"/>
-      <c r="BI19" s="78"/>
-      <c r="BJ19" s="80"/>
-      <c r="BK19" s="62"/>
-      <c r="BL19" s="63"/>
-      <c r="BM19" s="64"/>
+        <v>1</v>
+      </c>
+      <c r="I19" s="86"/>
+      <c r="J19" s="86"/>
+      <c r="K19" s="86"/>
+      <c r="L19" s="86"/>
+      <c r="M19" s="86"/>
+      <c r="N19" s="86"/>
+      <c r="O19" s="86"/>
+      <c r="P19" s="86"/>
+      <c r="Q19" s="86"/>
+      <c r="R19" s="86"/>
+      <c r="S19" s="86"/>
+      <c r="T19" s="86"/>
+      <c r="U19" s="86"/>
+      <c r="V19" s="86"/>
+      <c r="W19" s="86"/>
+      <c r="X19" s="86"/>
+      <c r="Y19" s="86"/>
+      <c r="Z19" s="86"/>
+      <c r="AA19" s="86"/>
+      <c r="AB19" s="86"/>
+      <c r="AC19" s="86"/>
+      <c r="AD19" s="86"/>
+      <c r="AE19" s="86"/>
+      <c r="AF19" s="86"/>
+      <c r="AG19" s="86"/>
+      <c r="AH19" s="86"/>
+      <c r="AI19" s="86"/>
+      <c r="AJ19" s="86"/>
+      <c r="AK19" s="86"/>
+      <c r="AL19" s="86"/>
+      <c r="AM19" s="86"/>
+      <c r="AN19" s="86"/>
+      <c r="AO19" s="87"/>
+      <c r="AP19" s="86"/>
+      <c r="AQ19" s="86"/>
+      <c r="AR19" s="87"/>
+      <c r="AS19" s="86"/>
+      <c r="AT19" s="86"/>
+      <c r="AU19" s="86"/>
+      <c r="AV19" s="88"/>
+      <c r="AW19" s="86"/>
+      <c r="AX19" s="86"/>
+      <c r="AY19" s="89"/>
+      <c r="AZ19" s="89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA19" s="86"/>
+      <c r="BB19" s="86"/>
+      <c r="BC19" s="88"/>
+      <c r="BD19" s="86"/>
+      <c r="BE19" s="86"/>
+      <c r="BF19" s="86"/>
+      <c r="BG19" s="86"/>
+      <c r="BH19" s="86"/>
+      <c r="BI19" s="90"/>
+      <c r="BJ19" s="91"/>
+      <c r="BK19" s="65"/>
+      <c r="BL19" s="66"/>
+      <c r="BM19" s="67"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
@@ -5543,7 +5999,7 @@
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="B19:D19"/>
   </mergeCells>
-  <conditionalFormatting sqref="I11:AC15 AE11:BF12 I19:BF19 AL16:BF16 AL17:AM17 AO17:BF17 I1:BF10 AD13:BF14 AE15:BF15 I16:AE16 AG16:AJ16 I17:AG17 I18:AJ18 AI17:AJ17 AL18:BF18">
+  <conditionalFormatting sqref="I11:AC15 AE11:BF12 I19:BF19 AL16:BF16 AO17:BF17 I2:BF10 AD13:BF14 I1:I10 J1:BJ1 AE15:BF15 I16:AE16 AG16:AJ16 I17:AG17 I18:AJ18 AL17:AM17 AI17:AJ17 AN18:BF18">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>IF(OR(WEEKDAY(I$1)=7,WEEKDAY(I$1)=1),1,0)</formula>
     </cfRule>
@@ -5553,7 +6009,7 @@
       <formula>IF(H2&lt;&gt;G2,TRUE())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I11:AC15 AE11:BF12 I19:BF19 AL16:BF16 AL17:AM17 AO17:BF17 I2:BF10 AD13:BF14 AE15:BF15 I16:AE16 AG16:AJ16 I17:AG17 I18:AJ18 AI17:AJ17 AL18:BF18">
+  <conditionalFormatting sqref="I11:AC15 AE11:BF12 I19:BF19 AL16:BF16 AO17:BF17 I2:BF10 AD13:BF14 AE15:BF15 I16:AE16 AG16:AJ16 I17:AG17 I18:AJ18 AL17:AM17 AI17:AJ17 AN18:BF18">
     <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>1</formula>
     </cfRule>
@@ -5565,5 +6021,6 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>